--- a/PREF_CRM_Web_Project_Plan_v6.xlsx
+++ b/PREF_CRM_Web_Project_Plan_v6.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Version Control" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Project Plan'!$A$1:$N$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Project Plan'!$A$1:$N$128</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Gantt Chart'!$A$1:$F$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -653,7 +653,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>v6.0</t>
+          <t>v6.1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>46168</v>
+        <v>46182</v>
       </c>
       <c r="C11" t="inlineStr"/>
     </row>
@@ -745,7 +745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N129"/>
+  <dimension ref="A1:N128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1079,15 +1079,15 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>MSG91 OTP integration (mobile auth backend)</t>
+          <t>Google SSO configuration (Gmail-based users)</t>
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Backend Dev</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -1097,36 +1097,32 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>Navneet</t>
+          <t>Prakash</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>OTP send + verify endpoints live for Flutter app</t>
+          <t>Gmail users land in Frappe via OAuth without password</t>
         </is>
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>Pre-UAT</t>
+          <t>UAT-1</t>
         </is>
       </c>
       <c r="K6" s="8" t="n">
-        <v>45907</v>
+        <v>46168</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>45909</v>
-      </c>
-      <c r="M6" s="8" t="n">
-        <v>45907</v>
-      </c>
-      <c r="N6" s="8" t="n">
-        <v>45909</v>
-      </c>
+        <v>46170</v>
+      </c>
+      <c r="M6" s="7" t="n"/>
+      <c r="N6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -1139,30 +1135,30 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Google SSO configuration (Gmail-based users)</t>
+          <t>Welcome email custom template (set-password link)</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>Backend Dev</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Prakash</t>
+          <t>Navneet</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Gmail users land in Frappe via OAuth without password</t>
+          <t>New users receive role-aware welcome email with set-password link</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
@@ -1176,7 +1172,7 @@
         </is>
       </c>
       <c r="K7" s="8" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="L7" s="8" t="n">
         <v>46170</v>
@@ -1185,118 +1181,122 @@
       <c r="N7" s="7" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="n">
+      <c r="A8" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Welcome email custom template (set-password link)</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>Backend Dev</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>Navneet</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>New users receive role-aware welcome email with set-password link</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>User Management</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>Developer / Tech Lead</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>Navneet</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>Core Team IT can add users, assign roles + blocks; users can log in</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
         <is>
           <t>UAT-1</t>
         </is>
       </c>
-      <c r="K8" s="8" t="n">
-        <v>46169</v>
-      </c>
-      <c r="L8" s="8" t="n">
+      <c r="K8" s="10" t="n">
+        <v>45940</v>
+      </c>
+      <c r="L8" s="10" t="n">
         <v>46170</v>
       </c>
-      <c r="M8" s="7" t="n"/>
-      <c r="N8" s="7" t="n"/>
+      <c r="M8" s="10" t="n">
+        <v>45940</v>
+      </c>
+      <c r="N8" s="9" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="n">
+      <c r="A9" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>User Management</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>Developer / Tech Lead</t>
-        </is>
-      </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Add User form (6 fields: name, email, phone, role, district, block)</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>Frontend Dev</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>Navneet</t>
-        </is>
-      </c>
-      <c r="H9" s="9" t="inlineStr">
-        <is>
-          <t>Core Team IT can add users, assign roles + blocks; users can log in</t>
-        </is>
-      </c>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="J9" s="9" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Navneet</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>Form validates + creates Frappe User + assigns role; BRD PR-XC-001 (UAT-1 verified: add/list/edit/deactivate PASS)</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>UAT-1</t>
         </is>
       </c>
-      <c r="K9" s="10" t="n">
+      <c r="K9" s="8" t="n">
         <v>45940</v>
       </c>
-      <c r="L9" s="10" t="n">
-        <v>46170</v>
-      </c>
-      <c r="M9" s="10" t="n">
+      <c r="L9" s="8" t="n">
+        <v>46180</v>
+      </c>
+      <c r="M9" s="8" t="n">
         <v>45940</v>
       </c>
-      <c r="N9" s="9" t="n"/>
+      <c r="N9" s="8" t="n">
+        <v>46180</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -1304,40 +1304,40 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Role assignment logic (6 roles -&gt; sidebar menu)</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>Tech Lead</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
           <t>2.1</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Add User form (6 fields: name, email, phone, role, district, block)</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>Frontend Dev</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>Navneet</t>
+          <t>Bhushan</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>Form validates + creates Frappe User + assigns role; BRD PR-XC-001</t>
+          <t>Each role lands on its own workspace; sidebar items hidden per role (UAT-1 verified for Field User nav)</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="J10" s="7" t="inlineStr">
@@ -1346,15 +1346,17 @@
         </is>
       </c>
       <c r="K10" s="8" t="n">
-        <v>45940</v>
+        <v>45942</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>46170</v>
+        <v>46180</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>45940</v>
-      </c>
-      <c r="N10" s="7" t="n"/>
+        <v>45942</v>
+      </c>
+      <c r="N10" s="8" t="n">
+        <v>46180</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -1362,40 +1364,40 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Role assignment logic (6 roles -&gt; sidebar menu)</t>
+          <t>Login flow: email + password</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>Tech Lead</t>
+          <t>Backend Dev</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>Bhushan</t>
+          <t>Navneet</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>Each role lands on its own workspace; sidebar items hidden per role</t>
+          <t>Standard Frappe login active for non-Gmail users</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="J11" s="7" t="inlineStr">
@@ -1404,15 +1406,17 @@
         </is>
       </c>
       <c r="K11" s="8" t="n">
-        <v>45942</v>
+        <v>45945</v>
       </c>
       <c r="L11" s="8" t="n">
-        <v>46170</v>
+        <v>45946</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>45942</v>
-      </c>
-      <c r="N11" s="7" t="n"/>
+        <v>45945</v>
+      </c>
+      <c r="N11" s="8" t="n">
+        <v>45946</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -1420,12 +1424,12 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Login flow: email + password</t>
+          <t>Login flow: Google SSO for Gmail users</t>
         </is>
       </c>
       <c r="D12" s="7" t="n">
@@ -1433,27 +1437,27 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Backend Dev</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>Navneet</t>
+          <t>Prakash</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>Standard Frappe login active for non-Gmail users</t>
+          <t>Gmail users log in via Google button</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="J12" s="7" t="inlineStr">
@@ -1462,17 +1466,13 @@
         </is>
       </c>
       <c r="K12" s="8" t="n">
-        <v>45945</v>
+        <v>46169</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>45946</v>
-      </c>
-      <c r="M12" s="8" t="n">
-        <v>45945</v>
-      </c>
-      <c r="N12" s="8" t="n">
-        <v>45946</v>
-      </c>
+        <v>46170</v>
+      </c>
+      <c r="M12" s="7" t="n"/>
+      <c r="N12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Login flow: Google SSO for Gmail users</t>
+          <t>Block assignment for Fessociates -&gt; auto-fill District/Block</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
@@ -1493,22 +1493,22 @@
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>Backend Dev</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Prakash</t>
+          <t>Navneet</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>Gmail users log in via Google button</t>
+          <t>Fessociate sees only their block's EPs; admin can override</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
@@ -1536,12 +1536,12 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Block assignment for Fessociates -&gt; auto-fill District/Block</t>
+          <t>District Coordinator: view-all edit-none permission set</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
@@ -1549,22 +1549,22 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Backend Dev</t>
+          <t>Tech Lead</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>Navneet</t>
+          <t>Bhushan</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>Fessociate sees only their block's EPs; admin can override</t>
+          <t>DC can browse all data but Save buttons disabled per role rule</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
@@ -1592,12 +1592,12 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>District Coordinator: view-all edit-none permission set</t>
+          <t>Designer role: restricted sidebar + upload-only permissions</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>DC can browse all data but Save buttons disabled per role rule</t>
+          <t>Designer sees only Logo/Label/Brochure draft upload screens</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
@@ -1648,12 +1648,12 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Designer role: restricted sidebar + upload-only permissions</t>
+          <t>SELCO Executive role: restricted to Infrastructure EE tab</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>Designer sees only Logo/Label/Brochure draft upload screens</t>
+          <t>SELCO sees only EE pricing entry + solarisation approval flow</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
@@ -1699,119 +1699,123 @@
       <c r="N16" s="7" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>2.8</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>SELCO Executive role: restricted to Infrastructure EE tab</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>Tech Lead</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>Bhushan</t>
-        </is>
-      </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>SELCO sees only EE pricing entry + solarisation approval flow</t>
-        </is>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Masters</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Developer / Tech Lead</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>Navneet</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>All seed masters loaded + linked across the doctype graph</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>UAT-1</t>
         </is>
       </c>
-      <c r="K17" s="8" t="n">
-        <v>46169</v>
-      </c>
-      <c r="L17" s="8" t="n">
-        <v>46170</v>
-      </c>
-      <c r="M17" s="7" t="n"/>
-      <c r="N17" s="7" t="n"/>
+      <c r="K17" s="6" t="n">
+        <v>45915</v>
+      </c>
+      <c r="L17" s="6" t="n">
+        <v>45935</v>
+      </c>
+      <c r="M17" s="6" t="n">
+        <v>45915</v>
+      </c>
+      <c r="N17" s="6" t="n">
+        <v>45935</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Masters</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>Developer / Tech Lead</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>District + Block + Village master (Meghalaya hierarchy)</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>Backend Dev</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>Navneet</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>All seed masters loaded + linked across the doctype graph</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>Navneet</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>All Meghalaya districts/blocks/villages loaded + cascading lookup live</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="J18" s="7" t="inlineStr">
         <is>
           <t>UAT-1</t>
         </is>
       </c>
-      <c r="K18" s="6" t="n">
+      <c r="K18" s="8" t="n">
         <v>45915</v>
       </c>
-      <c r="L18" s="6" t="n">
-        <v>45935</v>
-      </c>
-      <c r="M18" s="6" t="n">
+      <c r="L18" s="8" t="n">
+        <v>45918</v>
+      </c>
+      <c r="M18" s="8" t="n">
         <v>45915</v>
       </c>
-      <c r="N18" s="6" t="n">
-        <v>45935</v>
+      <c r="N18" s="8" t="n">
+        <v>45918</v>
       </c>
     </row>
     <row r="19">
@@ -1820,16 +1824,16 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>District + Block + Village master (Meghalaya hierarchy)</t>
+          <t>Sector + Business Basket + Product Type masters</t>
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
@@ -1848,7 +1852,7 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>All Meghalaya districts/blocks/villages loaded + cascading lookup live</t>
+          <t>Sector picker cascades to Business Basket then Product Type</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
@@ -1862,16 +1866,16 @@
         </is>
       </c>
       <c r="K19" s="8" t="n">
-        <v>45915</v>
+        <v>45919</v>
       </c>
       <c r="L19" s="8" t="n">
-        <v>45918</v>
+        <v>45920</v>
       </c>
       <c r="M19" s="8" t="n">
-        <v>45915</v>
+        <v>45919</v>
       </c>
       <c r="N19" s="8" t="n">
-        <v>45918</v>
+        <v>45920</v>
       </c>
     </row>
     <row r="20">
@@ -1880,16 +1884,16 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Sector + Business Basket + Product Type masters</t>
+          <t>Cohort master</t>
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
@@ -1908,7 +1912,7 @@
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>Sector picker cascades to Business Basket then Product Type</t>
+          <t>Cohort picker available on EP Profile</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
@@ -1922,16 +1926,16 @@
         </is>
       </c>
       <c r="K20" s="8" t="n">
-        <v>45919</v>
+        <v>45921</v>
       </c>
       <c r="L20" s="8" t="n">
-        <v>45920</v>
+        <v>45921</v>
       </c>
       <c r="M20" s="8" t="n">
-        <v>45919</v>
+        <v>45921</v>
       </c>
       <c r="N20" s="8" t="n">
-        <v>45920</v>
+        <v>45921</v>
       </c>
     </row>
     <row r="21">
@@ -1940,12 +1944,12 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Cohort master</t>
+          <t>Packaging master (12 types: Glass Jar ... Other)</t>
         </is>
       </c>
       <c r="D21" s="7" t="n">
@@ -1968,7 +1972,7 @@
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>Cohort picker available on EP Profile</t>
+          <t>All 12 packaging types selectable in Packaging framework</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
@@ -1982,16 +1986,16 @@
         </is>
       </c>
       <c r="K21" s="8" t="n">
-        <v>45921</v>
+        <v>45922</v>
       </c>
       <c r="L21" s="8" t="n">
-        <v>45921</v>
+        <v>45922</v>
       </c>
       <c r="M21" s="8" t="n">
-        <v>45921</v>
+        <v>45922</v>
       </c>
       <c r="N21" s="8" t="n">
-        <v>45921</v>
+        <v>45922</v>
       </c>
     </row>
     <row r="22">
@@ -2000,16 +2004,16 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Packaging master (12 types: Glass Jar ... Other)</t>
+          <t>Registration master (20 registration types)</t>
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
@@ -2028,7 +2032,7 @@
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>All 12 packaging types selectable in Packaging framework</t>
+          <t>All 20 registration types selectable in Registration framework</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
@@ -2042,16 +2046,16 @@
         </is>
       </c>
       <c r="K22" s="8" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="L22" s="8" t="n">
-        <v>45922</v>
+        <v>45925</v>
       </c>
       <c r="M22" s="8" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="N22" s="8" t="n">
-        <v>45922</v>
+        <v>45925</v>
       </c>
     </row>
     <row r="23">
@@ -2060,16 +2064,16 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Registration master (20 registration types)</t>
+          <t>Test Type master (14 test types)</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
@@ -2088,7 +2092,7 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>All 20 registration types selectable in Registration framework</t>
+          <t>Test type picker live in Product Testing framework</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
@@ -2102,16 +2106,16 @@
         </is>
       </c>
       <c r="K23" s="8" t="n">
-        <v>45923</v>
+        <v>45926</v>
       </c>
       <c r="L23" s="8" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="M23" s="8" t="n">
-        <v>45923</v>
+        <v>45926</v>
       </c>
       <c r="N23" s="8" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
     </row>
     <row r="24">
@@ -2120,12 +2124,12 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Test Type master (14 test types)</t>
+          <t>Lab master (12 labs)</t>
         </is>
       </c>
       <c r="D24" s="7" t="n">
@@ -2148,7 +2152,7 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>Test type picker live in Product Testing framework</t>
+          <t>Lab picker live in Product Testing framework</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
@@ -2162,16 +2166,16 @@
         </is>
       </c>
       <c r="K24" s="8" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="L24" s="8" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="M24" s="8" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="N24" s="8" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
     </row>
     <row r="25">
@@ -2180,12 +2184,12 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Lab master (12 labs)</t>
+          <t>Standardisation Type master (13 types)</t>
         </is>
       </c>
       <c r="D25" s="7" t="n">
@@ -2208,7 +2212,7 @@
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>Lab picker live in Product Testing framework</t>
+          <t>All 13 SOP types selectable in Standardization framework</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr">
@@ -2222,16 +2226,16 @@
         </is>
       </c>
       <c r="K25" s="8" t="n">
-        <v>45927</v>
+        <v>45928</v>
       </c>
       <c r="L25" s="8" t="n">
-        <v>45927</v>
+        <v>45928</v>
       </c>
       <c r="M25" s="8" t="n">
-        <v>45927</v>
+        <v>45928</v>
       </c>
       <c r="N25" s="8" t="n">
-        <v>45927</v>
+        <v>45928</v>
       </c>
     </row>
     <row r="26">
@@ -2240,16 +2244,16 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Standardisation Type master (13 types)</t>
+          <t>Scheme master (17 govt schemes)</t>
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
@@ -2268,7 +2272,7 @@
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>All 13 SOP types selectable in Standardization framework</t>
+          <t>All 17 schemes selectable in Funding framework</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
@@ -2282,16 +2286,16 @@
         </is>
       </c>
       <c r="K26" s="8" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="L26" s="8" t="n">
-        <v>45928</v>
+        <v>45930</v>
       </c>
       <c r="M26" s="8" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="N26" s="8" t="n">
-        <v>45928</v>
+        <v>45930</v>
       </c>
     </row>
     <row r="27">
@@ -2300,177 +2304,177 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Scheme master (17 govt schemes)</t>
+          <t>Role setup: 6 roles with permission rules</t>
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
+          <t>Tech Lead</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>Bhushan</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>Core IT, Core Prog, Fessociate, Designer, SELCO, DC roles created with default permissions</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>UAT-1</t>
+        </is>
+      </c>
+      <c r="K27" s="8" t="n">
+        <v>45931</v>
+      </c>
+      <c r="L27" s="8" t="n">
+        <v>45935</v>
+      </c>
+      <c r="M27" s="8" t="n">
+        <v>45931</v>
+      </c>
+      <c r="N27" s="8" t="n">
+        <v>45935</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Entrepreneur Profile</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>Navneet</t>
+        </is>
+      </c>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>Fessociates can create + maintain entrepreneur records end-to-end</t>
+        </is>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="inlineStr">
+        <is>
+          <t>UAT-1</t>
+        </is>
+      </c>
+      <c r="K28" s="10" t="n">
+        <v>45936</v>
+      </c>
+      <c r="L28" s="10" t="n">
+        <v>46170</v>
+      </c>
+      <c r="M28" s="10" t="n">
+        <v>45936</v>
+      </c>
+      <c r="N28" s="9" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>EP doctype backend (all fields + naming rule)</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
           <t>Backend Dev</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>Navneet</t>
-        </is>
-      </c>
-      <c r="H27" s="7" t="inlineStr">
-        <is>
-          <t>All 17 schemes selectable in Funding framework</t>
-        </is>
-      </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>Navneet</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>EP-{name}-##### naming; all fields validated server-side</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="J27" s="7" t="inlineStr">
+      <c r="J29" s="7" t="inlineStr">
         <is>
           <t>UAT-1</t>
         </is>
       </c>
-      <c r="K27" s="8" t="n">
-        <v>45929</v>
-      </c>
-      <c r="L27" s="8" t="n">
-        <v>45930</v>
-      </c>
-      <c r="M27" s="8" t="n">
-        <v>45929</v>
-      </c>
-      <c r="N27" s="8" t="n">
-        <v>45930</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>Role setup: 6 roles with permission rules</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>Tech Lead</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>Bhushan</t>
-        </is>
-      </c>
-      <c r="H28" s="7" t="inlineStr">
-        <is>
-          <t>Core IT, Core Prog, Fessociate, Designer, SELCO, DC roles created with default permissions</t>
-        </is>
-      </c>
-      <c r="I28" s="7" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="J28" s="7" t="inlineStr">
-        <is>
-          <t>UAT-1</t>
-        </is>
-      </c>
-      <c r="K28" s="8" t="n">
-        <v>45931</v>
-      </c>
-      <c r="L28" s="8" t="n">
-        <v>45935</v>
-      </c>
-      <c r="M28" s="8" t="n">
-        <v>45931</v>
-      </c>
-      <c r="N28" s="8" t="n">
-        <v>45935</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>Entrepreneur Profile</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="n">
-        <v>31</v>
-      </c>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>Developer</t>
-        </is>
-      </c>
-      <c r="F29" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G29" s="9" t="inlineStr">
-        <is>
-          <t>Navneet</t>
-        </is>
-      </c>
-      <c r="H29" s="9" t="inlineStr">
-        <is>
-          <t>Fessociates can create + maintain entrepreneur records end-to-end</t>
-        </is>
-      </c>
-      <c r="I29" s="9" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="J29" s="9" t="inlineStr">
-        <is>
-          <t>UAT-1</t>
-        </is>
-      </c>
-      <c r="K29" s="10" t="n">
+      <c r="K29" s="8" t="n">
         <v>45936</v>
       </c>
-      <c r="L29" s="10" t="n">
-        <v>46170</v>
-      </c>
-      <c r="M29" s="10" t="n">
+      <c r="L29" s="8" t="n">
+        <v>45940</v>
+      </c>
+      <c r="M29" s="8" t="n">
         <v>45936</v>
       </c>
-      <c r="N29" s="9" t="n"/>
+      <c r="N29" s="8" t="n">
+        <v>45940</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -2478,27 +2482,27 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>Vue: Profile Dashboard (9 sub-components)</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>Frontend Dev</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>EP doctype backend (all fields + naming rule)</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>Backend Dev</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
           <t>Navneet</t>
@@ -2506,7 +2510,7 @@
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>EP-{name}-##### naming; all fields validated server-side</t>
+          <t>Single-page entrepreneur view with stats + product shelf + DF rollup</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
@@ -2520,16 +2524,16 @@
         </is>
       </c>
       <c r="K30" s="8" t="n">
-        <v>45936</v>
+        <v>45942</v>
       </c>
       <c r="L30" s="8" t="n">
-        <v>45940</v>
+        <v>45950</v>
       </c>
       <c r="M30" s="8" t="n">
-        <v>45936</v>
+        <v>45942</v>
       </c>
       <c r="N30" s="8" t="n">
-        <v>45940</v>
+        <v>45950</v>
       </c>
     </row>
     <row r="31">
@@ -2538,27 +2542,27 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Vue: Selection tab (10 rating fields + Rural E-Champ)</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>Frontend Dev</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
           <t>4.2</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
-        <is>
-          <t>Vue: Profile Dashboard (9 sub-components)</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>Frontend Dev</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
           <t>Navneet</t>
@@ -2566,7 +2570,7 @@
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>Single-page entrepreneur view with stats + product shelf + DF rollup</t>
+          <t>Average rating auto-calculates; Rural E-Champ flag works</t>
         </is>
       </c>
       <c r="I31" s="7" t="inlineStr">
@@ -2580,16 +2584,16 @@
         </is>
       </c>
       <c r="K31" s="8" t="n">
-        <v>45942</v>
+        <v>45951</v>
       </c>
       <c r="L31" s="8" t="n">
-        <v>45950</v>
+        <v>45953</v>
       </c>
       <c r="M31" s="8" t="n">
-        <v>45942</v>
+        <v>45951</v>
       </c>
       <c r="N31" s="8" t="n">
-        <v>45950</v>
+        <v>45953</v>
       </c>
     </row>
     <row r="32">
@@ -2598,16 +2602,16 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Vue: Selection tab (10 rating fields + Rural E-Champ)</t>
+          <t>Vue: Prioritisation tab</t>
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
@@ -2626,7 +2630,7 @@
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>Average rating auto-calculates; Rural E-Champ flag works</t>
+          <t>Cards reorder on dashboard by priority value</t>
         </is>
       </c>
       <c r="I32" s="7" t="inlineStr">
@@ -2640,16 +2644,16 @@
         </is>
       </c>
       <c r="K32" s="8" t="n">
-        <v>45951</v>
+        <v>45954</v>
       </c>
       <c r="L32" s="8" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="M32" s="8" t="n">
-        <v>45951</v>
+        <v>45954</v>
       </c>
       <c r="N32" s="8" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
     </row>
     <row r="33">
@@ -2658,16 +2662,16 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Vue: Prioritisation tab</t>
+          <t>Vue: Location &amp; Contact + Geolocation pin</t>
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
@@ -2686,7 +2690,7 @@
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>Cards reorder on dashboard by priority value</t>
+          <t>Map pin saved; reverse-geocode populates district/block</t>
         </is>
       </c>
       <c r="I33" s="7" t="inlineStr">
@@ -2700,16 +2704,16 @@
         </is>
       </c>
       <c r="K33" s="8" t="n">
-        <v>45954</v>
+        <v>45955</v>
       </c>
       <c r="L33" s="8" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="M33" s="8" t="n">
-        <v>45954</v>
+        <v>45955</v>
       </c>
       <c r="N33" s="8" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
     </row>
     <row r="34">
@@ -2718,16 +2722,16 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Vue: Location &amp; Contact + Geolocation pin</t>
+          <t>Vue: Documents tab + photo gallery</t>
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
@@ -2746,7 +2750,7 @@
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>Map pin saved; reverse-geocode populates district/block</t>
+          <t>Documents upload + preview + lightbox gallery</t>
         </is>
       </c>
       <c r="I34" s="7" t="inlineStr">
@@ -2760,16 +2764,16 @@
         </is>
       </c>
       <c r="K34" s="8" t="n">
-        <v>45955</v>
+        <v>45958</v>
       </c>
       <c r="L34" s="8" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="M34" s="8" t="n">
-        <v>45955</v>
+        <v>45958</v>
       </c>
       <c r="N34" s="8" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
     </row>
     <row r="35">
@@ -2778,16 +2782,16 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Vue: Documents tab + photo gallery</t>
+          <t>Vue: Networking &amp; Mentoring tab (inline intro + meeting log)</t>
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
@@ -2806,7 +2810,7 @@
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>Documents upload + preview + lightbox gallery</t>
+          <t>PR feat/networking-mentoring-v2 merged; auto-sync meeting counts to parent</t>
         </is>
       </c>
       <c r="I35" s="7" t="inlineStr">
@@ -2820,16 +2824,16 @@
         </is>
       </c>
       <c r="K35" s="8" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>45958</v>
+        <v>45966</v>
       </c>
       <c r="M35" s="8" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="N35" s="8" t="n">
-        <v>45958</v>
+        <v>45966</v>
       </c>
     </row>
     <row r="36">
@@ -2838,16 +2842,16 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Vue: Networking &amp; Mentoring tab (inline intro + meeting log)</t>
+          <t>Vue: Intervention Logs (read-only sync from Activity Logger)</t>
         </is>
       </c>
       <c r="D36" s="7" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
@@ -2856,7 +2860,7 @@
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
@@ -2866,147 +2870,147 @@
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>PR feat/networking-mentoring-v2 merged; auto-sync meeting counts to parent</t>
+          <t>Every Activity Logger entry surfaces on EP timeline read-only</t>
         </is>
       </c>
       <c r="I36" s="7" t="inlineStr">
         <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="J36" s="7" t="inlineStr">
+        <is>
+          <t>UAT-1</t>
+        </is>
+      </c>
+      <c r="K36" s="8" t="n">
+        <v>45967</v>
+      </c>
+      <c r="L36" s="8" t="n">
+        <v>46170</v>
+      </c>
+      <c r="M36" s="8" t="n">
+        <v>45967</v>
+      </c>
+      <c r="N36" s="7" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>Product Profile</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>28</v>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>Navneet</t>
+        </is>
+      </c>
+      <c r="H37" s="9" t="inlineStr">
+        <is>
+          <t>All entrepreneur products captured with variants, process flow + production capacity</t>
+        </is>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="J37" s="9" t="inlineStr">
+        <is>
+          <t>UAT-1</t>
+        </is>
+      </c>
+      <c r="K37" s="10" t="n">
+        <v>45967</v>
+      </c>
+      <c r="L37" s="10" t="n">
+        <v>46170</v>
+      </c>
+      <c r="M37" s="10" t="n">
+        <v>45967</v>
+      </c>
+      <c r="N37" s="9" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>Product doctype backend + child tables</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>Backend Dev</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>Navneet</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>Product + variant + process step doctypes deployed</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="J36" s="7" t="inlineStr">
+      <c r="J38" s="7" t="inlineStr">
         <is>
           <t>UAT-1</t>
         </is>
       </c>
-      <c r="K36" s="8" t="n">
-        <v>45959</v>
-      </c>
-      <c r="L36" s="8" t="n">
-        <v>45966</v>
-      </c>
-      <c r="M36" s="8" t="n">
-        <v>45959</v>
-      </c>
-      <c r="N36" s="8" t="n">
-        <v>45966</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>4.8</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>Vue: Intervention Logs (read-only sync from Activity Logger)</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>Frontend Dev</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="inlineStr">
-        <is>
-          <t>Navneet</t>
-        </is>
-      </c>
-      <c r="H37" s="7" t="inlineStr">
-        <is>
-          <t>Every Activity Logger entry surfaces on EP timeline read-only</t>
-        </is>
-      </c>
-      <c r="I37" s="7" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="J37" s="7" t="inlineStr">
-        <is>
-          <t>UAT-1</t>
-        </is>
-      </c>
-      <c r="K37" s="8" t="n">
+      <c r="K38" s="8" t="n">
         <v>45967</v>
       </c>
-      <c r="L37" s="8" t="n">
-        <v>46170</v>
-      </c>
-      <c r="M37" s="8" t="n">
+      <c r="L38" s="8" t="n">
+        <v>45969</v>
+      </c>
+      <c r="M38" s="8" t="n">
         <v>45967</v>
       </c>
-      <c r="N37" s="7" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="9" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>Product Profile</t>
-        </is>
-      </c>
-      <c r="D38" s="9" t="n">
-        <v>28</v>
-      </c>
-      <c r="E38" s="9" t="inlineStr">
-        <is>
-          <t>Developer</t>
-        </is>
-      </c>
-      <c r="F38" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G38" s="9" t="inlineStr">
-        <is>
-          <t>Navneet</t>
-        </is>
-      </c>
-      <c r="H38" s="9" t="inlineStr">
-        <is>
-          <t>All entrepreneur products captured with variants, process flow + production capacity</t>
-        </is>
-      </c>
-      <c r="I38" s="9" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="J38" s="9" t="inlineStr">
-        <is>
-          <t>UAT-1</t>
-        </is>
-      </c>
-      <c r="K38" s="10" t="n">
-        <v>45967</v>
-      </c>
-      <c r="L38" s="10" t="n">
-        <v>46170</v>
-      </c>
-      <c r="M38" s="10" t="n">
-        <v>45967</v>
-      </c>
-      <c r="N38" s="9" t="n"/>
+      <c r="N38" s="8" t="n">
+        <v>45969</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -3014,27 +3018,27 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>Vue: Product Details tab (12 fields)</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>Frontend Dev</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
           <t>5.1</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>Product doctype backend + child tables</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>Backend Dev</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
           <t>Navneet</t>
@@ -3042,7 +3046,7 @@
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>Product + variant + process step doctypes deployed</t>
+          <t>Form populates + saves; product type integration live</t>
         </is>
       </c>
       <c r="I39" s="7" t="inlineStr">
@@ -3056,16 +3060,16 @@
         </is>
       </c>
       <c r="K39" s="8" t="n">
-        <v>45967</v>
+        <v>45970</v>
       </c>
       <c r="L39" s="8" t="n">
-        <v>45969</v>
+        <v>45976</v>
       </c>
       <c r="M39" s="8" t="n">
-        <v>45967</v>
+        <v>45970</v>
       </c>
       <c r="N39" s="8" t="n">
-        <v>45969</v>
+        <v>45976</v>
       </c>
     </row>
     <row r="40">
@@ -3074,16 +3078,16 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Vue: Product Details tab (12 fields)</t>
+          <t>Vue: Product Variants tab (SKU auto-gen + volume calc)</t>
         </is>
       </c>
       <c r="D40" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
@@ -3102,7 +3106,7 @@
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>Form populates + saves; product type integration live</t>
+          <t>SKU = VARIANT-SUBVARIANT-WEIGHT-UNIT; volume = LxBxH auto</t>
         </is>
       </c>
       <c r="I40" s="7" t="inlineStr">
@@ -3116,16 +3120,16 @@
         </is>
       </c>
       <c r="K40" s="8" t="n">
-        <v>45970</v>
+        <v>45977</v>
       </c>
       <c r="L40" s="8" t="n">
-        <v>45976</v>
+        <v>45983</v>
       </c>
       <c r="M40" s="8" t="n">
-        <v>45970</v>
+        <v>45977</v>
       </c>
       <c r="N40" s="8" t="n">
-        <v>45976</v>
+        <v>45983</v>
       </c>
     </row>
     <row r="41">
@@ -3134,16 +3138,16 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Vue: Product Variants tab (SKU auto-gen + volume calc)</t>
+          <t>Vue: Process Flow tab (drag-drop reorderable steps)</t>
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
@@ -3162,7 +3166,7 @@
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>SKU = VARIANT-SUBVARIANT-WEIGHT-UNIT; volume = LxBxH auto</t>
+          <t>Drag-drop reorders + saves; machine + flow master linked</t>
         </is>
       </c>
       <c r="I41" s="7" t="inlineStr">
@@ -3176,16 +3180,16 @@
         </is>
       </c>
       <c r="K41" s="8" t="n">
-        <v>45977</v>
+        <v>45984</v>
       </c>
       <c r="L41" s="8" t="n">
-        <v>45983</v>
+        <v>45989</v>
       </c>
       <c r="M41" s="8" t="n">
-        <v>45977</v>
+        <v>45984</v>
       </c>
       <c r="N41" s="8" t="n">
-        <v>45983</v>
+        <v>45989</v>
       </c>
     </row>
     <row r="42">
@@ -3194,16 +3198,16 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Vue: Process Flow tab (drag-drop reorderable steps)</t>
+          <t>Vue: Production Capacity tab (agri-conditional + monthly tracker)</t>
         </is>
       </c>
       <c r="D42" s="7" t="n">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
@@ -3212,7 +3216,7 @@
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
@@ -3222,12 +3226,12 @@
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>Drag-drop reorders + saves; machine + flow master linked</t>
+          <t>Available Months x Variants matrix renders + saves per-variant qty</t>
         </is>
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="J42" s="7" t="inlineStr">
@@ -3236,17 +3240,15 @@
         </is>
       </c>
       <c r="K42" s="8" t="n">
-        <v>45984</v>
+        <v>45990</v>
       </c>
       <c r="L42" s="8" t="n">
-        <v>45989</v>
+        <v>46170</v>
       </c>
       <c r="M42" s="8" t="n">
-        <v>45984</v>
-      </c>
-      <c r="N42" s="8" t="n">
-        <v>45989</v>
-      </c>
+        <v>45990</v>
+      </c>
+      <c r="N42" s="7" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -3254,27 +3256,27 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
+          <t>5.6</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>Available Months checkbox logic -&gt; tracker generation</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>Frontend Dev</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
           <t>5.5</t>
         </is>
       </c>
-      <c r="C43" s="7" t="inlineStr">
-        <is>
-          <t>Vue: Production Capacity tab (agri-conditional + monthly tracker)</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="n">
-        <v>60</v>
-      </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>Frontend Dev</t>
-        </is>
-      </c>
-      <c r="F43" s="7" t="inlineStr">
-        <is>
-          <t>5.3</t>
-        </is>
-      </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
           <t>Navneet</t>
@@ -3282,7 +3284,7 @@
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>Available Months x Variants matrix renders + saves per-variant qty</t>
+          <t>Selecting months auto-creates corresponding columns in tracker</t>
         </is>
       </c>
       <c r="I43" s="7" t="inlineStr">
@@ -3296,131 +3298,133 @@
         </is>
       </c>
       <c r="K43" s="8" t="n">
-        <v>45990</v>
+        <v>45992</v>
       </c>
       <c r="L43" s="8" t="n">
         <v>46170</v>
       </c>
       <c r="M43" s="8" t="n">
-        <v>45990</v>
+        <v>45992</v>
       </c>
       <c r="N43" s="7" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="7" t="n">
+      <c r="A44" s="9" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>5.6</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="inlineStr">
-        <is>
-          <t>Available Months checkbox logic -&gt; tracker generation</t>
-        </is>
-      </c>
-      <c r="D44" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="E44" s="7" t="inlineStr">
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>Diagnostic Frameworks (27)</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="n">
+        <v>130</v>
+      </c>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="F44" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G44" s="9" t="inlineStr">
+        <is>
+          <t>Navneet</t>
+        </is>
+      </c>
+      <c r="H44" s="9" t="inlineStr">
+        <is>
+          <t>All 27 framework forms deployed; entrepreneurs can be diagnosed end-to-end</t>
+        </is>
+      </c>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="J44" s="9" t="inlineStr">
+        <is>
+          <t>UAT-1</t>
+        </is>
+      </c>
+      <c r="K44" s="10" t="n">
+        <v>45992</v>
+      </c>
+      <c r="L44" s="10" t="n">
+        <v>46170</v>
+      </c>
+      <c r="M44" s="10" t="n">
+        <v>45992</v>
+      </c>
+      <c r="N44" s="9" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>Manufacturing - Raw Materials</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
         <is>
           <t>Frontend Dev</t>
         </is>
       </c>
-      <c r="F44" s="7" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="G44" s="7" t="inlineStr">
-        <is>
-          <t>Navneet</t>
-        </is>
-      </c>
-      <c r="H44" s="7" t="inlineStr">
-        <is>
-          <t>Selecting months auto-creates corresponding columns in tracker</t>
-        </is>
-      </c>
-      <c r="I44" s="7" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="J44" s="7" t="inlineStr">
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>Navneet</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>Existing + Required tabs with Cost/Batch calc + Summary</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="J45" s="7" t="inlineStr">
         <is>
           <t>UAT-1</t>
         </is>
       </c>
-      <c r="K44" s="8" t="n">
+      <c r="K45" s="8" t="n">
         <v>45992</v>
       </c>
-      <c r="L44" s="8" t="n">
-        <v>46170</v>
-      </c>
-      <c r="M44" s="8" t="n">
+      <c r="L45" s="8" t="n">
+        <v>45996</v>
+      </c>
+      <c r="M45" s="8" t="n">
         <v>45992</v>
       </c>
-      <c r="N44" s="7" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="9" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C45" s="9" t="inlineStr">
-        <is>
-          <t>Diagnostic Frameworks (27)</t>
-        </is>
-      </c>
-      <c r="D45" s="9" t="n">
-        <v>130</v>
-      </c>
-      <c r="E45" s="9" t="inlineStr">
-        <is>
-          <t>Developer</t>
-        </is>
-      </c>
-      <c r="F45" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G45" s="9" t="inlineStr">
-        <is>
-          <t>Navneet</t>
-        </is>
-      </c>
-      <c r="H45" s="9" t="inlineStr">
-        <is>
-          <t>All 27 framework forms deployed; entrepreneurs can be diagnosed end-to-end</t>
-        </is>
-      </c>
-      <c r="I45" s="9" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="J45" s="9" t="inlineStr">
-        <is>
-          <t>UAT-1</t>
-        </is>
-      </c>
-      <c r="K45" s="10" t="n">
-        <v>45992</v>
-      </c>
-      <c r="L45" s="10" t="n">
-        <v>46170</v>
-      </c>
-      <c r="M45" s="10" t="n">
-        <v>45992</v>
-      </c>
-      <c r="N45" s="9" t="n"/>
+      <c r="N45" s="8" t="n">
+        <v>45996</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -3428,12 +3432,12 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>Manufacturing - Raw Materials</t>
+          <t>Manufacturing - Machinery</t>
         </is>
       </c>
       <c r="D46" s="7" t="n">
@@ -3456,7 +3460,7 @@
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>Existing + Required tabs with Cost/Batch calc + Summary</t>
+          <t>22 fields + 7 calcs + depreciation + solarisation flags</t>
         </is>
       </c>
       <c r="I46" s="7" t="inlineStr">
@@ -3470,16 +3474,16 @@
         </is>
       </c>
       <c r="K46" s="8" t="n">
-        <v>45992</v>
+        <v>45997</v>
       </c>
       <c r="L46" s="8" t="n">
-        <v>45996</v>
+        <v>46001</v>
       </c>
       <c r="M46" s="8" t="n">
-        <v>45992</v>
+        <v>45997</v>
       </c>
       <c r="N46" s="8" t="n">
-        <v>45996</v>
+        <v>46001</v>
       </c>
     </row>
     <row r="47">
@@ -3488,16 +3492,16 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>Manufacturing - Machinery</t>
+          <t>Manufacturing - Human Resource</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
@@ -3516,7 +3520,7 @@
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>22 fields + 7 calcs + depreciation + solarisation flags</t>
+          <t>3 wage formulas + GoM compliance warnings + 8 intervention types</t>
         </is>
       </c>
       <c r="I47" s="7" t="inlineStr">
@@ -3530,16 +3534,16 @@
         </is>
       </c>
       <c r="K47" s="8" t="n">
-        <v>45997</v>
+        <v>46002</v>
       </c>
       <c r="L47" s="8" t="n">
-        <v>46001</v>
+        <v>46005</v>
       </c>
       <c r="M47" s="8" t="n">
-        <v>45997</v>
+        <v>46002</v>
       </c>
       <c r="N47" s="8" t="n">
-        <v>46001</v>
+        <v>46005</v>
       </c>
     </row>
     <row r="48">
@@ -3548,16 +3552,16 @@
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>Manufacturing - Human Resource</t>
+          <t>Pricing - Unit Pricing</t>
         </is>
       </c>
       <c r="D48" s="7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
@@ -3566,7 +3570,7 @@
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6.1,6.2,6.3</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
@@ -3576,7 +3580,7 @@
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>3 wage formulas + GoM compliance warnings + 8 intervention types</t>
+          <t>9-section cost buildup + 3 pricing methods x 2 channels</t>
         </is>
       </c>
       <c r="I48" s="7" t="inlineStr">
@@ -3590,16 +3594,16 @@
         </is>
       </c>
       <c r="K48" s="8" t="n">
-        <v>46002</v>
+        <v>46006</v>
       </c>
       <c r="L48" s="8" t="n">
-        <v>46005</v>
+        <v>46013</v>
       </c>
       <c r="M48" s="8" t="n">
-        <v>46002</v>
+        <v>46006</v>
       </c>
       <c r="N48" s="8" t="n">
-        <v>46005</v>
+        <v>46013</v>
       </c>
     </row>
     <row r="49">
@@ -3608,16 +3612,16 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>Pricing - Unit Pricing</t>
+          <t>Market - Market Research</t>
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>8</v>
+        <v>158</v>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
@@ -3626,7 +3630,7 @@
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>6.1,6.2,6.3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
@@ -3636,12 +3640,12 @@
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>9-section cost buildup + 3 pricing methods x 2 channels</t>
+          <t>4 sections + competitive pricing + SWOT (auto-avg cross-feed pending)</t>
         </is>
       </c>
       <c r="I49" s="7" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="J49" s="7" t="inlineStr">
@@ -3650,17 +3654,15 @@
         </is>
       </c>
       <c r="K49" s="8" t="n">
-        <v>46006</v>
+        <v>46014</v>
       </c>
       <c r="L49" s="8" t="n">
-        <v>46013</v>
+        <v>46170</v>
       </c>
       <c r="M49" s="8" t="n">
-        <v>46006</v>
-      </c>
-      <c r="N49" s="8" t="n">
-        <v>46013</v>
-      </c>
+        <v>46014</v>
+      </c>
+      <c r="N49" s="7" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
@@ -3668,16 +3670,16 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>Market - Market Research</t>
+          <t>Market - Customer Analysis</t>
         </is>
       </c>
       <c r="D50" s="7" t="n">
-        <v>158</v>
+        <v>4</v>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
@@ -3696,12 +3698,12 @@
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
-          <t>4 sections + competitive pricing + SWOT (auto-avg cross-feed pending)</t>
+          <t>6 segmentations + Existing/Required intervention toggles</t>
         </is>
       </c>
       <c r="I50" s="7" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="J50" s="7" t="inlineStr">
@@ -3710,15 +3712,17 @@
         </is>
       </c>
       <c r="K50" s="8" t="n">
-        <v>46014</v>
+        <v>46017</v>
       </c>
       <c r="L50" s="8" t="n">
-        <v>46170</v>
+        <v>46020</v>
       </c>
       <c r="M50" s="8" t="n">
-        <v>46014</v>
-      </c>
-      <c r="N50" s="7" t="n"/>
+        <v>46017</v>
+      </c>
+      <c r="N50" s="8" t="n">
+        <v>46020</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n">
@@ -3726,12 +3730,12 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>Market - Customer Analysis</t>
+          <t>Market - Market Linkage</t>
         </is>
       </c>
       <c r="D51" s="7" t="n">
@@ -3754,7 +3758,7 @@
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
-          <t>6 segmentations + Existing/Required intervention toggles</t>
+          <t>Channel revenue tracking + annualized revenue calc</t>
         </is>
       </c>
       <c r="I51" s="7" t="inlineStr">
@@ -3768,16 +3772,16 @@
         </is>
       </c>
       <c r="K51" s="8" t="n">
-        <v>46017</v>
+        <v>46021</v>
       </c>
       <c r="L51" s="8" t="n">
-        <v>46020</v>
+        <v>46024</v>
       </c>
       <c r="M51" s="8" t="n">
-        <v>46017</v>
+        <v>46021</v>
       </c>
       <c r="N51" s="8" t="n">
-        <v>46020</v>
+        <v>46024</v>
       </c>
     </row>
     <row r="52">
@@ -3786,16 +3790,16 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>Market - Market Linkage</t>
+          <t>Market - Promotions</t>
         </is>
       </c>
       <c r="D52" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
@@ -3814,7 +3818,7 @@
       </c>
       <c r="H52" s="7" t="inlineStr">
         <is>
-          <t>Channel revenue tracking + annualized revenue calc</t>
+          <t>Existing + Required table with channel/mode/platform + frequency</t>
         </is>
       </c>
       <c r="I52" s="7" t="inlineStr">
@@ -3828,16 +3832,16 @@
         </is>
       </c>
       <c r="K52" s="8" t="n">
-        <v>46021</v>
+        <v>46025</v>
       </c>
       <c r="L52" s="8" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="M52" s="8" t="n">
-        <v>46021</v>
+        <v>46025</v>
       </c>
       <c r="N52" s="8" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
     </row>
     <row r="53">
@@ -3846,16 +3850,16 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>Market - Promotions</t>
+          <t>Product Dev - Registration &amp; Licensing</t>
         </is>
       </c>
       <c r="D53" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
@@ -3874,7 +3878,7 @@
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>Existing + Required table with channel/mode/platform + frequency</t>
+          <t>20-type master + Lifetime Validity conditional + status chips + 5-status pipeline</t>
         </is>
       </c>
       <c r="I53" s="7" t="inlineStr">
@@ -3888,16 +3892,16 @@
         </is>
       </c>
       <c r="K53" s="8" t="n">
-        <v>46025</v>
+        <v>46028</v>
       </c>
       <c r="L53" s="8" t="n">
-        <v>46027</v>
+        <v>46032</v>
       </c>
       <c r="M53" s="8" t="n">
-        <v>46025</v>
+        <v>46028</v>
       </c>
       <c r="N53" s="8" t="n">
-        <v>46027</v>
+        <v>46032</v>
       </c>
     </row>
     <row r="54">
@@ -3906,16 +3910,16 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>Product Dev - Registration &amp; Licensing</t>
+          <t>Product Dev - Prototyping</t>
         </is>
       </c>
       <c r="D54" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
@@ -3934,12 +3938,12 @@
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>20-type master + Lifetime Validity conditional + status chips + 5-status pipeline</t>
+          <t>Conditional dropdown + iteration child table [Bug 54 P1: cannot save - server 500 on framework_name; REGRESSED in UAT-1]</t>
         </is>
       </c>
       <c r="I54" s="7" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="J54" s="7" t="inlineStr">
@@ -3948,17 +3952,15 @@
         </is>
       </c>
       <c r="K54" s="8" t="n">
-        <v>46028</v>
+        <v>46033</v>
       </c>
       <c r="L54" s="8" t="n">
-        <v>46032</v>
+        <v>46036</v>
       </c>
       <c r="M54" s="8" t="n">
-        <v>46028</v>
-      </c>
-      <c r="N54" s="8" t="n">
-        <v>46032</v>
-      </c>
+        <v>46033</v>
+      </c>
+      <c r="N54" s="7" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
@@ -3966,12 +3968,12 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>Product Dev - Prototyping</t>
+          <t>Product Dev - Testing</t>
         </is>
       </c>
       <c r="D55" s="7" t="n">
@@ -3994,7 +3996,7 @@
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
-          <t>Conditional dropdown (Packaging/Product) + iteration child table</t>
+          <t>14 test types + 12 labs + consent management + date chain validation</t>
         </is>
       </c>
       <c r="I55" s="7" t="inlineStr">
@@ -4008,16 +4010,16 @@
         </is>
       </c>
       <c r="K55" s="8" t="n">
-        <v>46033</v>
+        <v>46037</v>
       </c>
       <c r="L55" s="8" t="n">
-        <v>46036</v>
+        <v>46040</v>
       </c>
       <c r="M55" s="8" t="n">
-        <v>46033</v>
+        <v>46037</v>
       </c>
       <c r="N55" s="8" t="n">
-        <v>46036</v>
+        <v>46040</v>
       </c>
     </row>
     <row r="56">
@@ -4026,12 +4028,12 @@
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>Product Dev - Testing</t>
+          <t>Product Dev - Standardization</t>
         </is>
       </c>
       <c r="D56" s="7" t="n">
@@ -4054,7 +4056,7 @@
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>14 test types + 12 labs + consent management + date chain validation</t>
+          <t>13 SOP types + auto Product Sector + version tracking</t>
         </is>
       </c>
       <c r="I56" s="7" t="inlineStr">
@@ -4068,16 +4070,16 @@
         </is>
       </c>
       <c r="K56" s="8" t="n">
-        <v>46037</v>
+        <v>46041</v>
       </c>
       <c r="L56" s="8" t="n">
-        <v>46040</v>
+        <v>46044</v>
       </c>
       <c r="M56" s="8" t="n">
-        <v>46037</v>
+        <v>46041</v>
       </c>
       <c r="N56" s="8" t="n">
-        <v>46040</v>
+        <v>46044</v>
       </c>
     </row>
     <row r="57">
@@ -4086,16 +4088,16 @@
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>Product Dev - Standardization</t>
+          <t>Product Dev - Quality Control</t>
         </is>
       </c>
       <c r="D57" s="7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
@@ -4114,7 +4116,7 @@
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
-          <t>13 SOP types + auto Product Sector + version tracking</t>
+          <t>23-question star rating + average + maturity tier + distribution chart</t>
         </is>
       </c>
       <c r="I57" s="7" t="inlineStr">
@@ -4128,16 +4130,16 @@
         </is>
       </c>
       <c r="K57" s="8" t="n">
-        <v>46041</v>
+        <v>46045</v>
       </c>
       <c r="L57" s="8" t="n">
-        <v>46044</v>
+        <v>46050</v>
       </c>
       <c r="M57" s="8" t="n">
-        <v>46041</v>
+        <v>46045</v>
       </c>
       <c r="N57" s="8" t="n">
-        <v>46044</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="58">
@@ -4146,16 +4148,16 @@
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>Product Dev - Quality Control</t>
+          <t>Product Dev - Packaging</t>
         </is>
       </c>
       <c r="D58" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
@@ -4174,7 +4176,7 @@
       </c>
       <c r="H58" s="7" t="inlineStr">
         <is>
-          <t>23-question star rating + average + maturity tier + distribution chart</t>
+          <t>Per-variant detail + monthly qty matrix + sealing multi-select</t>
         </is>
       </c>
       <c r="I58" s="7" t="inlineStr">
@@ -4188,16 +4190,16 @@
         </is>
       </c>
       <c r="K58" s="8" t="n">
-        <v>46045</v>
+        <v>46051</v>
       </c>
       <c r="L58" s="8" t="n">
-        <v>46050</v>
+        <v>46057</v>
       </c>
       <c r="M58" s="8" t="n">
-        <v>46045</v>
+        <v>46051</v>
       </c>
       <c r="N58" s="8" t="n">
-        <v>46050</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="59">
@@ -4206,16 +4208,16 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>Product Dev - Packaging</t>
+          <t>Marketing Tools - Brand Name</t>
         </is>
       </c>
       <c r="D59" s="7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
@@ -4234,7 +4236,7 @@
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>Per-variant detail + monthly qty matrix + sealing multi-select</t>
+          <t>Dual approval flow + market scope chips + log book</t>
         </is>
       </c>
       <c r="I59" s="7" t="inlineStr">
@@ -4248,16 +4250,16 @@
         </is>
       </c>
       <c r="K59" s="8" t="n">
-        <v>46051</v>
+        <v>46058</v>
       </c>
       <c r="L59" s="8" t="n">
-        <v>46057</v>
+        <v>46061</v>
       </c>
       <c r="M59" s="8" t="n">
-        <v>46051</v>
+        <v>46058</v>
       </c>
       <c r="N59" s="8" t="n">
-        <v>46057</v>
+        <v>46061</v>
       </c>
     </row>
     <row r="60">
@@ -4266,27 +4268,27 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
+          <t>6.16</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>Marketing Tools - Logo</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>Frontend Dev</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
           <t>6.15</t>
         </is>
       </c>
-      <c r="C60" s="7" t="inlineStr">
-        <is>
-          <t>Marketing Tools - Brand Name</t>
-        </is>
-      </c>
-      <c r="D60" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E60" s="7" t="inlineStr">
-        <is>
-          <t>Frontend Dev</t>
-        </is>
-      </c>
-      <c r="F60" s="7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
           <t>Navneet</t>
@@ -4294,7 +4296,7 @@
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
-          <t>Dual approval flow + market scope chips + log book</t>
+          <t>Designer assignment + 3 drafts + dual approval</t>
         </is>
       </c>
       <c r="I60" s="7" t="inlineStr">
@@ -4308,16 +4310,16 @@
         </is>
       </c>
       <c r="K60" s="8" t="n">
-        <v>46058</v>
+        <v>46062</v>
       </c>
       <c r="L60" s="8" t="n">
-        <v>46061</v>
+        <v>46064</v>
       </c>
       <c r="M60" s="8" t="n">
-        <v>46058</v>
+        <v>46062</v>
       </c>
       <c r="N60" s="8" t="n">
-        <v>46061</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="61">
@@ -4326,12 +4328,12 @@
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>Marketing Tools - Logo</t>
+          <t>Marketing Tools - Business Card</t>
         </is>
       </c>
       <c r="D61" s="7" t="n">
@@ -4354,7 +4356,7 @@
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>Designer assignment + 3 drafts + dual approval</t>
+          <t>Auto-populated content + QR uploads</t>
         </is>
       </c>
       <c r="I61" s="7" t="inlineStr">
@@ -4368,16 +4370,16 @@
         </is>
       </c>
       <c r="K61" s="8" t="n">
-        <v>46062</v>
+        <v>46065</v>
       </c>
       <c r="L61" s="8" t="n">
-        <v>46064</v>
+        <v>46067</v>
       </c>
       <c r="M61" s="8" t="n">
-        <v>46062</v>
+        <v>46065</v>
       </c>
       <c r="N61" s="8" t="n">
-        <v>46064</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="62">
@@ -4386,16 +4388,16 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>Marketing Tools - Business Card</t>
+          <t>Marketing Tools - Label</t>
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>3</v>
+        <v>102</v>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
@@ -4404,7 +4406,7 @@
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
@@ -4414,12 +4416,12 @@
       </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
-          <t>Auto-populated content + QR uploads</t>
+          <t>Per-variant table + AI Generate storyline (Apoorva dep) + 5-status pipeline</t>
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="J62" s="7" t="inlineStr">
@@ -4428,17 +4430,15 @@
         </is>
       </c>
       <c r="K62" s="8" t="n">
-        <v>46065</v>
+        <v>46068</v>
       </c>
       <c r="L62" s="8" t="n">
-        <v>46067</v>
+        <v>46170</v>
       </c>
       <c r="M62" s="8" t="n">
-        <v>46065</v>
-      </c>
-      <c r="N62" s="8" t="n">
-        <v>46067</v>
-      </c>
+        <v>46068</v>
+      </c>
+      <c r="N62" s="7" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n">
@@ -4446,16 +4446,16 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>Marketing Tools - Label</t>
+          <t>Marketing Tools - Brochure</t>
         </is>
       </c>
       <c r="D63" s="7" t="n">
-        <v>102</v>
+        <v>5</v>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
@@ -4474,12 +4474,12 @@
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>Per-variant table + AI Generate storyline (Apoorva dep) + 5-status pipeline</t>
+          <t>Brochure setup + product listings + status + log book</t>
         </is>
       </c>
       <c r="I63" s="7" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="J63" s="7" t="inlineStr">
@@ -4488,15 +4488,17 @@
         </is>
       </c>
       <c r="K63" s="8" t="n">
-        <v>46068</v>
+        <v>46075</v>
       </c>
       <c r="L63" s="8" t="n">
-        <v>46170</v>
+        <v>46079</v>
       </c>
       <c r="M63" s="8" t="n">
-        <v>46068</v>
-      </c>
-      <c r="N63" s="7" t="n"/>
+        <v>46075</v>
+      </c>
+      <c r="N63" s="8" t="n">
+        <v>46079</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
@@ -4504,16 +4506,16 @@
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>Marketing Tools - Brochure</t>
+          <t>Skilling - Digital Literacy</t>
         </is>
       </c>
       <c r="D64" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
@@ -4532,7 +4534,7 @@
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>Brochure setup + product listings + status + log book</t>
+          <t>Access &amp; Devices + 9-platform star rating + intervention flags</t>
         </is>
       </c>
       <c r="I64" s="7" t="inlineStr">
@@ -4546,16 +4548,16 @@
         </is>
       </c>
       <c r="K64" s="8" t="n">
-        <v>46075</v>
+        <v>46080</v>
       </c>
       <c r="L64" s="8" t="n">
-        <v>46079</v>
+        <v>46083</v>
       </c>
       <c r="M64" s="8" t="n">
-        <v>46075</v>
+        <v>46080</v>
       </c>
       <c r="N64" s="8" t="n">
-        <v>46079</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="65">
@@ -4564,16 +4566,16 @@
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>Skilling - Digital Literacy</t>
+          <t>Skilling - Capacity Building</t>
         </is>
       </c>
       <c r="D65" s="7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
@@ -4592,7 +4594,7 @@
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
-          <t>Access &amp; Devices + 9-platform star rating + intervention flags</t>
+          <t>Scorecard Gap calc + Past Trainings (6-dim stars) + Required gap analysis</t>
         </is>
       </c>
       <c r="I65" s="7" t="inlineStr">
@@ -4606,16 +4608,16 @@
         </is>
       </c>
       <c r="K65" s="8" t="n">
-        <v>46080</v>
+        <v>46084</v>
       </c>
       <c r="L65" s="8" t="n">
-        <v>46083</v>
+        <v>46089</v>
       </c>
       <c r="M65" s="8" t="n">
-        <v>46080</v>
+        <v>46084</v>
       </c>
       <c r="N65" s="8" t="n">
-        <v>46083</v>
+        <v>46089</v>
       </c>
     </row>
     <row r="66">
@@ -4624,16 +4626,16 @@
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>Skilling - Capacity Building</t>
+          <t>Skilling - Business Plan Canvas</t>
         </is>
       </c>
       <c r="D66" s="7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
@@ -4652,7 +4654,7 @@
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>Scorecard Gap calc + Past Trainings (6-dim stars) + Required gap analysis</t>
+          <t>9 Canvas sections + SWOT (BPC HTML pending from client)</t>
         </is>
       </c>
       <c r="I66" s="7" t="inlineStr">
@@ -4666,16 +4668,16 @@
         </is>
       </c>
       <c r="K66" s="8" t="n">
-        <v>46084</v>
+        <v>46090</v>
       </c>
       <c r="L66" s="8" t="n">
-        <v>46089</v>
+        <v>46092</v>
       </c>
       <c r="M66" s="8" t="n">
-        <v>46084</v>
+        <v>46090</v>
       </c>
       <c r="N66" s="8" t="n">
-        <v>46089</v>
+        <v>46092</v>
       </c>
     </row>
     <row r="67">
@@ -4684,16 +4686,16 @@
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>Skilling - Business Plan Canvas</t>
+          <t>Logistics - Packing</t>
         </is>
       </c>
       <c r="D67" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
@@ -4712,7 +4714,7 @@
       </c>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>9 Canvas sections + SWOT (BPC HTML pending from client)</t>
+          <t>Per-product transit packaging + monthly volume + cost calc</t>
         </is>
       </c>
       <c r="I67" s="7" t="inlineStr">
@@ -4726,16 +4728,16 @@
         </is>
       </c>
       <c r="K67" s="8" t="n">
-        <v>46090</v>
+        <v>46093</v>
       </c>
       <c r="L67" s="8" t="n">
-        <v>46092</v>
+        <v>46097</v>
       </c>
       <c r="M67" s="8" t="n">
-        <v>46090</v>
+        <v>46093</v>
       </c>
       <c r="N67" s="8" t="n">
-        <v>46092</v>
+        <v>46097</v>
       </c>
     </row>
     <row r="68">
@@ -4744,12 +4746,12 @@
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>Logistics - Packing</t>
+          <t>Logistics - Service</t>
         </is>
       </c>
       <c r="D68" s="7" t="n">
@@ -4772,7 +4774,7 @@
       </c>
       <c r="H68" s="7" t="inlineStr">
         <is>
-          <t>Per-product transit packaging + monthly volume + cost calc</t>
+          <t>Connectivity + available services + route blocks with leg tables</t>
         </is>
       </c>
       <c r="I68" s="7" t="inlineStr">
@@ -4786,16 +4788,16 @@
         </is>
       </c>
       <c r="K68" s="8" t="n">
-        <v>46093</v>
+        <v>46098</v>
       </c>
       <c r="L68" s="8" t="n">
-        <v>46097</v>
+        <v>46102</v>
       </c>
       <c r="M68" s="8" t="n">
-        <v>46093</v>
+        <v>46098</v>
       </c>
       <c r="N68" s="8" t="n">
-        <v>46097</v>
+        <v>46102</v>
       </c>
     </row>
     <row r="69">
@@ -4804,16 +4806,16 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>Logistics - Service</t>
+          <t>Infrastructure (BE + EE + CE combined)</t>
         </is>
       </c>
       <c r="D69" s="7" t="n">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
@@ -4832,12 +4834,12 @@
       </c>
       <c r="H69" s="7" t="inlineStr">
         <is>
-          <t>Connectivity + available services + route blocks with leg tables</t>
+          <t>BE plinth rate + EE auto from machinery + CE solarisation + Financial Model (PRIME/Innovation)</t>
         </is>
       </c>
       <c r="I69" s="7" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="J69" s="7" t="inlineStr">
@@ -4846,17 +4848,15 @@
         </is>
       </c>
       <c r="K69" s="8" t="n">
-        <v>46098</v>
+        <v>46103</v>
       </c>
       <c r="L69" s="8" t="n">
-        <v>46102</v>
+        <v>46170</v>
       </c>
       <c r="M69" s="8" t="n">
-        <v>46098</v>
-      </c>
-      <c r="N69" s="8" t="n">
-        <v>46102</v>
-      </c>
+        <v>46103</v>
+      </c>
+      <c r="N69" s="7" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
@@ -4864,16 +4864,16 @@
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>Infrastructure (BE + EE + CE combined)</t>
+          <t>Funding - Pitch Deck</t>
         </is>
       </c>
       <c r="D70" s="7" t="n">
-        <v>67</v>
+        <v>3</v>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
@@ -4892,12 +4892,12 @@
       </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
-          <t>BE plinth rate + EE auto from machinery + CE solarisation + Financial Model (PRIME/Innovation)</t>
+          <t>Summary (X/11 progress) + Existing + Required (11 slides) + log book</t>
         </is>
       </c>
       <c r="I70" s="7" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="J70" s="7" t="inlineStr">
@@ -4906,15 +4906,17 @@
         </is>
       </c>
       <c r="K70" s="8" t="n">
-        <v>46103</v>
+        <v>46104</v>
       </c>
       <c r="L70" s="8" t="n">
-        <v>46170</v>
+        <v>46106</v>
       </c>
       <c r="M70" s="8" t="n">
-        <v>46103</v>
-      </c>
-      <c r="N70" s="7" t="n"/>
+        <v>46104</v>
+      </c>
+      <c r="N70" s="8" t="n">
+        <v>46106</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
@@ -4922,16 +4924,16 @@
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>Funding - Pitch Deck</t>
+          <t>Funding - Schemes</t>
         </is>
       </c>
       <c r="D71" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
@@ -4950,7 +4952,7 @@
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
-          <t>Summary (X/11 progress) + Existing + Required (11 slides) + log book</t>
+          <t>17-scheme master + loan details + EMI calc + Required pipeline</t>
         </is>
       </c>
       <c r="I71" s="7" t="inlineStr">
@@ -4964,135 +4966,135 @@
         </is>
       </c>
       <c r="K71" s="8" t="n">
-        <v>46104</v>
+        <v>46107</v>
       </c>
       <c r="L71" s="8" t="n">
-        <v>46106</v>
+        <v>46111</v>
       </c>
       <c r="M71" s="8" t="n">
-        <v>46104</v>
+        <v>46107</v>
       </c>
       <c r="N71" s="8" t="n">
-        <v>46106</v>
+        <v>46111</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="7" t="n">
+      <c r="A72" s="9" t="n">
         <v>71</v>
       </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>6.27</t>
-        </is>
-      </c>
-      <c r="C72" s="7" t="inlineStr">
-        <is>
-          <t>Funding - Schemes</t>
-        </is>
-      </c>
-      <c r="D72" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>Frontend Dev</t>
-        </is>
-      </c>
-      <c r="F72" s="7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G72" s="7" t="inlineStr">
-        <is>
-          <t>Navneet</t>
-        </is>
-      </c>
-      <c r="H72" s="7" t="inlineStr">
-        <is>
-          <t>17-scheme master + loan details + EMI calc + Required pipeline</t>
-        </is>
-      </c>
-      <c r="I72" s="7" t="inlineStr">
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>Research Notes</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E72" s="9" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="F72" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G72" s="9" t="inlineStr">
+        <is>
+          <t>Navneet</t>
+        </is>
+      </c>
+      <c r="H72" s="9" t="inlineStr">
+        <is>
+          <t>Fessociates can log free-form research notes; optional EP linking</t>
+        </is>
+      </c>
+      <c r="I72" s="9" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="J72" s="9" t="inlineStr">
+        <is>
+          <t>UAT-2</t>
+        </is>
+      </c>
+      <c r="K72" s="10" t="n">
+        <v>46099</v>
+      </c>
+      <c r="L72" s="10" t="n">
+        <v>46178</v>
+      </c>
+      <c r="M72" s="10" t="n">
+        <v>46099</v>
+      </c>
+      <c r="N72" s="9" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>Research Notes doctype backend</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>Backend Dev</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>Navneet</t>
+        </is>
+      </c>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
+          <t>Doctype with 11 fields deployed; permissions wired</t>
+        </is>
+      </c>
+      <c r="I73" s="7" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="J72" s="7" t="inlineStr">
-        <is>
-          <t>UAT-1</t>
-        </is>
-      </c>
-      <c r="K72" s="8" t="n">
-        <v>46107</v>
-      </c>
-      <c r="L72" s="8" t="n">
-        <v>46111</v>
-      </c>
-      <c r="M72" s="8" t="n">
-        <v>46107</v>
-      </c>
-      <c r="N72" s="8" t="n">
-        <v>46111</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="9" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" s="9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C73" s="9" t="inlineStr">
-        <is>
-          <t>Research Notes</t>
-        </is>
-      </c>
-      <c r="D73" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="E73" s="9" t="inlineStr">
-        <is>
-          <t>Developer</t>
-        </is>
-      </c>
-      <c r="F73" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G73" s="9" t="inlineStr">
-        <is>
-          <t>Navneet</t>
-        </is>
-      </c>
-      <c r="H73" s="9" t="inlineStr">
-        <is>
-          <t>Fessociates can log free-form research notes; optional EP linking</t>
-        </is>
-      </c>
-      <c r="I73" s="9" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="J73" s="9" t="inlineStr">
+      <c r="J73" s="7" t="inlineStr">
         <is>
           <t>UAT-2</t>
         </is>
       </c>
-      <c r="K73" s="10" t="n">
+      <c r="K73" s="8" t="n">
         <v>46099</v>
       </c>
-      <c r="L73" s="10" t="n">
-        <v>46178</v>
-      </c>
-      <c r="M73" s="10" t="n">
+      <c r="L73" s="8" t="n">
+        <v>46100</v>
+      </c>
+      <c r="M73" s="8" t="n">
         <v>46099</v>
       </c>
-      <c r="N73" s="9" t="n"/>
+      <c r="N73" s="8" t="n">
+        <v>46100</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
@@ -5100,27 +5102,27 @@
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>Vue: Research Notes form (11 fields)</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>Frontend Dev</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
           <t>7.1</t>
         </is>
       </c>
-      <c r="C74" s="7" t="inlineStr">
-        <is>
-          <t>Research Notes doctype backend</t>
-        </is>
-      </c>
-      <c r="D74" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E74" s="7" t="inlineStr">
-        <is>
-          <t>Backend Dev</t>
-        </is>
-      </c>
-      <c r="F74" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
           <t>Navneet</t>
@@ -5128,7 +5130,7 @@
       </c>
       <c r="H74" s="7" t="inlineStr">
         <is>
-          <t>Doctype with 11 fields deployed; permissions wired</t>
+          <t>Standard Frappe form with 11 fields renders + saves</t>
         </is>
       </c>
       <c r="I74" s="7" t="inlineStr">
@@ -5142,16 +5144,16 @@
         </is>
       </c>
       <c r="K74" s="8" t="n">
-        <v>46099</v>
+        <v>46101</v>
       </c>
       <c r="L74" s="8" t="n">
-        <v>46100</v>
+        <v>46104</v>
       </c>
       <c r="M74" s="8" t="n">
-        <v>46099</v>
+        <v>46101</v>
       </c>
       <c r="N74" s="8" t="n">
-        <v>46100</v>
+        <v>46104</v>
       </c>
     </row>
     <row r="75">
@@ -5160,25 +5162,25 @@
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>Vue: Research Notes form (11 fields)</t>
+          <t>EP Profile linking (optional)</t>
         </is>
       </c>
       <c r="D75" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>Frontend Dev</t>
+          <t>Backend Dev</t>
         </is>
       </c>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.1,4.1</t>
         </is>
       </c>
       <c r="G75" s="7" t="inlineStr">
@@ -5188,145 +5190,145 @@
       </c>
       <c r="H75" s="7" t="inlineStr">
         <is>
-          <t>Standard Frappe form with 11 fields renders + saves</t>
+          <t>Note can be tagged to an entrepreneur; surfaces on EP profile</t>
         </is>
       </c>
       <c r="I75" s="7" t="inlineStr">
         <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J75" s="7" t="inlineStr">
+        <is>
+          <t>UAT-2</t>
+        </is>
+      </c>
+      <c r="K75" s="8" t="n">
+        <v>46175</v>
+      </c>
+      <c r="L75" s="8" t="n">
+        <v>46178</v>
+      </c>
+      <c r="M75" s="7" t="n"/>
+      <c r="N75" s="7" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="9" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>Village Survey</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="E76" s="9" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="F76" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G76" s="9" t="inlineStr">
+        <is>
+          <t>Navneet</t>
+        </is>
+      </c>
+      <c r="H76" s="9" t="inlineStr">
+        <is>
+          <t>Village-level survey form complete; geo-pins ready for Landscape Map</t>
+        </is>
+      </c>
+      <c r="I76" s="9" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="J76" s="9" t="inlineStr">
+        <is>
+          <t>UAT-2</t>
+        </is>
+      </c>
+      <c r="K76" s="10" t="n">
+        <v>46105</v>
+      </c>
+      <c r="L76" s="10" t="n">
+        <v>46182</v>
+      </c>
+      <c r="M76" s="10" t="n">
+        <v>46105</v>
+      </c>
+      <c r="N76" s="9" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>Village Survey doctype backend</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>Backend Dev</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="inlineStr">
+        <is>
+          <t>Navneet</t>
+        </is>
+      </c>
+      <c r="H77" s="7" t="inlineStr">
+        <is>
+          <t>village_visit doctype with 16 picker child doctypes deployed</t>
+        </is>
+      </c>
+      <c r="I77" s="7" t="inlineStr">
+        <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="J75" s="7" t="inlineStr">
+      <c r="J77" s="7" t="inlineStr">
         <is>
           <t>UAT-2</t>
         </is>
       </c>
-      <c r="K75" s="8" t="n">
-        <v>46101</v>
-      </c>
-      <c r="L75" s="8" t="n">
-        <v>46104</v>
-      </c>
-      <c r="M75" s="8" t="n">
-        <v>46101</v>
-      </c>
-      <c r="N75" s="8" t="n">
-        <v>46104</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="7" t="n">
-        <v>75</v>
-      </c>
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t>7.3</t>
-        </is>
-      </c>
-      <c r="C76" s="7" t="inlineStr">
-        <is>
-          <t>EP Profile linking (optional)</t>
-        </is>
-      </c>
-      <c r="D76" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="E76" s="7" t="inlineStr">
-        <is>
-          <t>Backend Dev</t>
-        </is>
-      </c>
-      <c r="F76" s="7" t="inlineStr">
-        <is>
-          <t>7.1,4.1</t>
-        </is>
-      </c>
-      <c r="G76" s="7" t="inlineStr">
-        <is>
-          <t>Navneet</t>
-        </is>
-      </c>
-      <c r="H76" s="7" t="inlineStr">
-        <is>
-          <t>Note can be tagged to an entrepreneur; surfaces on EP profile</t>
-        </is>
-      </c>
-      <c r="I76" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J76" s="7" t="inlineStr">
-        <is>
-          <t>UAT-2</t>
-        </is>
-      </c>
-      <c r="K76" s="8" t="n">
-        <v>46175</v>
-      </c>
-      <c r="L76" s="8" t="n">
-        <v>46178</v>
-      </c>
-      <c r="M76" s="7" t="n"/>
-      <c r="N76" s="7" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="9" t="n">
-        <v>76</v>
-      </c>
-      <c r="B77" s="9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C77" s="9" t="inlineStr">
-        <is>
-          <t>Village Survey</t>
-        </is>
-      </c>
-      <c r="D77" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="E77" s="9" t="inlineStr">
-        <is>
-          <t>Developer</t>
-        </is>
-      </c>
-      <c r="F77" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G77" s="9" t="inlineStr">
-        <is>
-          <t>Navneet</t>
-        </is>
-      </c>
-      <c r="H77" s="9" t="inlineStr">
-        <is>
-          <t>Village-level survey form complete; geo-pins ready for Landscape Map</t>
-        </is>
-      </c>
-      <c r="I77" s="9" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="J77" s="9" t="inlineStr">
-        <is>
-          <t>UAT-2</t>
-        </is>
-      </c>
-      <c r="K77" s="10" t="n">
+      <c r="K77" s="8" t="n">
         <v>46105</v>
       </c>
-      <c r="L77" s="10" t="n">
-        <v>46182</v>
-      </c>
-      <c r="M77" s="10" t="n">
+      <c r="L77" s="8" t="n">
+        <v>46106</v>
+      </c>
+      <c r="M77" s="8" t="n">
         <v>46105</v>
       </c>
-      <c r="N77" s="9" t="n"/>
+      <c r="N77" s="8" t="n">
+        <v>46106</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
@@ -5334,27 +5336,27 @@
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>Vue: Survey form (17 fields + geolocation)</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>Frontend Dev</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="C78" s="7" t="inlineStr">
-        <is>
-          <t>Village Survey doctype backend</t>
-        </is>
-      </c>
-      <c r="D78" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E78" s="7" t="inlineStr">
-        <is>
-          <t>Backend Dev</t>
-        </is>
-      </c>
-      <c r="F78" s="7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
           <t>Navneet</t>
@@ -5362,7 +5364,7 @@
       </c>
       <c r="H78" s="7" t="inlineStr">
         <is>
-          <t>village_visit doctype with 16 picker child doctypes deployed</t>
+          <t>Form renders + saves; geolocation captured</t>
         </is>
       </c>
       <c r="I78" s="7" t="inlineStr">
@@ -5376,16 +5378,16 @@
         </is>
       </c>
       <c r="K78" s="8" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="L78" s="8" t="n">
-        <v>46106</v>
+        <v>46111</v>
       </c>
       <c r="M78" s="8" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="N78" s="8" t="n">
-        <v>46106</v>
+        <v>46111</v>
       </c>
     </row>
     <row r="79">
@@ -5394,12 +5396,12 @@
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>Vue: Survey form (17 fields + geolocation)</t>
+          <t>Master pickers: crops + forest resources + livelihoods (16 pickers)</t>
         </is>
       </c>
       <c r="D79" s="7" t="n">
@@ -5407,7 +5409,7 @@
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>Frontend Dev</t>
+          <t>Backend Dev</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
@@ -5422,7 +5424,7 @@
       </c>
       <c r="H79" s="7" t="inlineStr">
         <is>
-          <t>Form renders + saves; geolocation captured</t>
+          <t>All 16 picker doctypes loaded with seed data</t>
         </is>
       </c>
       <c r="I79" s="7" t="inlineStr">
@@ -5436,16 +5438,16 @@
         </is>
       </c>
       <c r="K79" s="8" t="n">
-        <v>46107</v>
+        <v>46112</v>
       </c>
       <c r="L79" s="8" t="n">
-        <v>46111</v>
+        <v>46116</v>
       </c>
       <c r="M79" s="8" t="n">
-        <v>46107</v>
+        <v>46112</v>
       </c>
       <c r="N79" s="8" t="n">
-        <v>46111</v>
+        <v>46116</v>
       </c>
     </row>
     <row r="80">
@@ -5454,16 +5456,16 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>Master pickers: crops + forest resources + livelihoods (16 pickers)</t>
+          <t>Geo-tag -&gt; Landscape Map integration (village pins)</t>
         </is>
       </c>
       <c r="D80" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
@@ -5472,7 +5474,7 @@
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2,10.1</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr">
@@ -5482,145 +5484,145 @@
       </c>
       <c r="H80" s="7" t="inlineStr">
         <is>
-          <t>All 16 picker doctypes loaded with seed data</t>
+          <t>Village pins render on Landscape Map with popup</t>
         </is>
       </c>
       <c r="I80" s="7" t="inlineStr">
         <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J80" s="7" t="inlineStr">
+        <is>
+          <t>UAT-2</t>
+        </is>
+      </c>
+      <c r="K80" s="8" t="n">
+        <v>46175</v>
+      </c>
+      <c r="L80" s="8" t="n">
+        <v>46182</v>
+      </c>
+      <c r="M80" s="7" t="n"/>
+      <c r="N80" s="7" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>Fellow Activity Logger</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="E81" s="9" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="F81" s="9" t="inlineStr">
+        <is>
+          <t>5,6</t>
+        </is>
+      </c>
+      <c r="G81" s="9" t="inlineStr">
+        <is>
+          <t>Navneet</t>
+        </is>
+      </c>
+      <c r="H81" s="9" t="inlineStr">
+        <is>
+          <t>Fessociates log activities (Calendar/Board) with cascading filters; sync to EP + Log Book</t>
+        </is>
+      </c>
+      <c r="I81" s="9" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="J81" s="9" t="inlineStr">
+        <is>
+          <t>UAT-1</t>
+        </is>
+      </c>
+      <c r="K81" s="10" t="n">
+        <v>46117</v>
+      </c>
+      <c r="L81" s="10" t="n">
+        <v>46170</v>
+      </c>
+      <c r="M81" s="10" t="n">
+        <v>46117</v>
+      </c>
+      <c r="N81" s="9" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>Replace Tasks workspace with Activity Logger pages</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>Frontend Dev</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t>5,6</t>
+        </is>
+      </c>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>Navneet</t>
+        </is>
+      </c>
+      <c r="H82" s="7" t="inlineStr">
+        <is>
+          <t>task_manager + task_manager_app + task_manager_grid pages deployed</t>
+        </is>
+      </c>
+      <c r="I82" s="7" t="inlineStr">
+        <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="J80" s="7" t="inlineStr">
-        <is>
-          <t>UAT-2</t>
-        </is>
-      </c>
-      <c r="K80" s="8" t="n">
-        <v>46112</v>
-      </c>
-      <c r="L80" s="8" t="n">
-        <v>46116</v>
-      </c>
-      <c r="M80" s="8" t="n">
-        <v>46112</v>
-      </c>
-      <c r="N80" s="8" t="n">
-        <v>46116</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="7" t="n">
-        <v>80</v>
-      </c>
-      <c r="B81" s="7" t="inlineStr">
-        <is>
-          <t>8.4</t>
-        </is>
-      </c>
-      <c r="C81" s="7" t="inlineStr">
-        <is>
-          <t>Geo-tag -&gt; Landscape Map integration (village pins)</t>
-        </is>
-      </c>
-      <c r="D81" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="E81" s="7" t="inlineStr">
-        <is>
-          <t>Backend Dev</t>
-        </is>
-      </c>
-      <c r="F81" s="7" t="inlineStr">
-        <is>
-          <t>8.2,10.1</t>
-        </is>
-      </c>
-      <c r="G81" s="7" t="inlineStr">
-        <is>
-          <t>Navneet</t>
-        </is>
-      </c>
-      <c r="H81" s="7" t="inlineStr">
-        <is>
-          <t>Village pins render on Landscape Map with popup</t>
-        </is>
-      </c>
-      <c r="I81" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J81" s="7" t="inlineStr">
-        <is>
-          <t>UAT-2</t>
-        </is>
-      </c>
-      <c r="K81" s="8" t="n">
-        <v>46175</v>
-      </c>
-      <c r="L81" s="8" t="n">
-        <v>46182</v>
-      </c>
-      <c r="M81" s="7" t="n"/>
-      <c r="N81" s="7" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="9" t="n">
-        <v>81</v>
-      </c>
-      <c r="B82" s="9" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C82" s="9" t="inlineStr">
-        <is>
-          <t>Fellow Activity Logger</t>
-        </is>
-      </c>
-      <c r="D82" s="9" t="n">
-        <v>60</v>
-      </c>
-      <c r="E82" s="9" t="inlineStr">
-        <is>
-          <t>Developer</t>
-        </is>
-      </c>
-      <c r="F82" s="9" t="inlineStr">
-        <is>
-          <t>5,6</t>
-        </is>
-      </c>
-      <c r="G82" s="9" t="inlineStr">
-        <is>
-          <t>Navneet</t>
-        </is>
-      </c>
-      <c r="H82" s="9" t="inlineStr">
-        <is>
-          <t>Fessociates log activities (Calendar/Board) with cascading filters; sync to EP + Log Book</t>
-        </is>
-      </c>
-      <c r="I82" s="9" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="J82" s="9" t="inlineStr">
+      <c r="J82" s="7" t="inlineStr">
         <is>
           <t>UAT-1</t>
         </is>
       </c>
-      <c r="K82" s="10" t="n">
+      <c r="K82" s="8" t="n">
         <v>46117</v>
       </c>
-      <c r="L82" s="10" t="n">
-        <v>46170</v>
-      </c>
-      <c r="M82" s="10" t="n">
+      <c r="L82" s="8" t="n">
+        <v>46120</v>
+      </c>
+      <c r="M82" s="8" t="n">
         <v>46117</v>
       </c>
-      <c r="N82" s="9" t="n"/>
+      <c r="N82" s="8" t="n">
+        <v>46120</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n">
@@ -5628,27 +5630,27 @@
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
+          <t>9.2</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>Vue: Calendar view (default)</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>Frontend Dev</t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="inlineStr">
+        <is>
           <t>9.1</t>
         </is>
       </c>
-      <c r="C83" s="7" t="inlineStr">
-        <is>
-          <t>Replace Tasks workspace with Activity Logger pages</t>
-        </is>
-      </c>
-      <c r="D83" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E83" s="7" t="inlineStr">
-        <is>
-          <t>Frontend Dev</t>
-        </is>
-      </c>
-      <c r="F83" s="7" t="inlineStr">
-        <is>
-          <t>5,6</t>
-        </is>
-      </c>
       <c r="G83" s="7" t="inlineStr">
         <is>
           <t>Navneet</t>
@@ -5656,7 +5658,7 @@
       </c>
       <c r="H83" s="7" t="inlineStr">
         <is>
-          <t>task_manager + task_manager_app + task_manager_grid pages deployed</t>
+          <t>TaskManagerApp.vue renders calendar with activities</t>
         </is>
       </c>
       <c r="I83" s="7" t="inlineStr">
@@ -5670,16 +5672,16 @@
         </is>
       </c>
       <c r="K83" s="8" t="n">
-        <v>46117</v>
+        <v>46121</v>
       </c>
       <c r="L83" s="8" t="n">
-        <v>46120</v>
+        <v>46127</v>
       </c>
       <c r="M83" s="8" t="n">
-        <v>46117</v>
+        <v>46121</v>
       </c>
       <c r="N83" s="8" t="n">
-        <v>46120</v>
+        <v>46127</v>
       </c>
     </row>
     <row r="84">
@@ -5688,16 +5690,16 @@
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>Vue: Calendar view (default)</t>
+          <t>Vue: Board view + toggle</t>
         </is>
       </c>
       <c r="D84" s="7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
@@ -5716,7 +5718,7 @@
       </c>
       <c r="H84" s="7" t="inlineStr">
         <is>
-          <t>TaskManagerApp.vue renders calendar with activities</t>
+          <t>TaskManagerGrid.vue renders board; toggle between board/calendar</t>
         </is>
       </c>
       <c r="I84" s="7" t="inlineStr">
@@ -5730,16 +5732,16 @@
         </is>
       </c>
       <c r="K84" s="8" t="n">
-        <v>46121</v>
+        <v>46128</v>
       </c>
       <c r="L84" s="8" t="n">
-        <v>46127</v>
+        <v>46131</v>
       </c>
       <c r="M84" s="8" t="n">
-        <v>46121</v>
+        <v>46128</v>
       </c>
       <c r="N84" s="8" t="n">
-        <v>46127</v>
+        <v>46131</v>
       </c>
     </row>
     <row r="85">
@@ -5748,16 +5750,16 @@
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>Vue: Board view + toggle</t>
+          <t>6 cascading filters (District -&gt; Block -&gt; EP -&gt; Module -&gt; Framework -&gt; Task)</t>
         </is>
       </c>
       <c r="D85" s="7" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
@@ -5766,7 +5768,7 @@
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="G85" s="7" t="inlineStr">
@@ -5776,12 +5778,12 @@
       </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
-          <t>TaskManagerGrid.vue renders board; toggle between board/calendar</t>
+          <t>All 6 levels cascade and reset downstream selections</t>
         </is>
       </c>
       <c r="I85" s="7" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="J85" s="7" t="inlineStr">
@@ -5790,17 +5792,15 @@
         </is>
       </c>
       <c r="K85" s="8" t="n">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="L85" s="8" t="n">
-        <v>46131</v>
+        <v>46170</v>
       </c>
       <c r="M85" s="8" t="n">
-        <v>46128</v>
-      </c>
-      <c r="N85" s="8" t="n">
-        <v>46131</v>
-      </c>
+        <v>46132</v>
+      </c>
+      <c r="N85" s="7" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n">
@@ -5808,16 +5808,16 @@
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>6 cascading filters (District -&gt; Block -&gt; EP -&gt; Module -&gt; Framework -&gt; Task)</t>
+          <t>Activity form: branching logic (3 paths: EP-Framework / EP-NonFramework / NonEntrepreneur)</t>
         </is>
       </c>
       <c r="D86" s="7" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="H86" s="7" t="inlineStr">
         <is>
-          <t>All 6 levels cascade and reset downstream selections</t>
+          <t>Activity form branches correctly based on entrepreneur + framework selection</t>
         </is>
       </c>
       <c r="I86" s="7" t="inlineStr">
@@ -5850,13 +5850,13 @@
         </is>
       </c>
       <c r="K86" s="8" t="n">
-        <v>46132</v>
+        <v>46136</v>
       </c>
       <c r="L86" s="8" t="n">
         <v>46170</v>
       </c>
       <c r="M86" s="8" t="n">
-        <v>46132</v>
+        <v>46136</v>
       </c>
       <c r="N86" s="7" t="n"/>
     </row>
@@ -5866,27 +5866,27 @@
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
+          <t>9.6</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>Sync: framework activities -&gt; Log Book tabs</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>Backend Dev</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
           <t>9.5</t>
         </is>
       </c>
-      <c r="C87" s="7" t="inlineStr">
-        <is>
-          <t>Activity form: branching logic (3 paths: EP-Framework / EP-NonFramework / NonEntrepreneur)</t>
-        </is>
-      </c>
-      <c r="D87" s="7" t="n">
-        <v>35</v>
-      </c>
-      <c r="E87" s="7" t="inlineStr">
-        <is>
-          <t>Frontend Dev</t>
-        </is>
-      </c>
-      <c r="F87" s="7" t="inlineStr">
-        <is>
-          <t>9.2</t>
-        </is>
-      </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
           <t>Navneet</t>
@@ -5894,28 +5894,26 @@
       </c>
       <c r="H87" s="7" t="inlineStr">
         <is>
-          <t>Activity form branches correctly based on entrepreneur + framework selection</t>
+          <t>Activity completion writes to corresponding framework Log Book</t>
         </is>
       </c>
       <c r="I87" s="7" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="J87" s="7" t="inlineStr">
         <is>
-          <t>UAT-1</t>
+          <t>UAT-2</t>
         </is>
       </c>
       <c r="K87" s="8" t="n">
-        <v>46136</v>
+        <v>46175</v>
       </c>
       <c r="L87" s="8" t="n">
-        <v>46170</v>
-      </c>
-      <c r="M87" s="8" t="n">
-        <v>46136</v>
-      </c>
+        <v>46179</v>
+      </c>
+      <c r="M87" s="7" t="n"/>
       <c r="N87" s="7" t="n"/>
     </row>
     <row r="88">
@@ -5924,12 +5922,12 @@
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>Sync: framework activities -&gt; Log Book tabs</t>
+          <t>Sync: all EP activities -&gt; Intervention Logs (read-only)</t>
         </is>
       </c>
       <c r="D88" s="7" t="n">
@@ -5942,7 +5940,7 @@
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.5,4.8</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr">
@@ -5952,7 +5950,7 @@
       </c>
       <c r="H88" s="7" t="inlineStr">
         <is>
-          <t>Activity completion writes to corresponding framework Log Book</t>
+          <t>EP Profile -&gt; Intervention Logs reflects every Activity Logger entry</t>
         </is>
       </c>
       <c r="I88" s="7" t="inlineStr">
@@ -5980,27 +5978,27 @@
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
+          <t>9.8</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>Framework completion tracking (Not Started -&gt; Completed -&gt; xN)</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>Backend Dev</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
           <t>9.7</t>
         </is>
       </c>
-      <c r="C89" s="7" t="inlineStr">
-        <is>
-          <t>Sync: all EP activities -&gt; Intervention Logs (read-only)</t>
-        </is>
-      </c>
-      <c r="D89" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="E89" s="7" t="inlineStr">
-        <is>
-          <t>Backend Dev</t>
-        </is>
-      </c>
-      <c r="F89" s="7" t="inlineStr">
-        <is>
-          <t>9.5,4.8</t>
-        </is>
-      </c>
       <c r="G89" s="7" t="inlineStr">
         <is>
           <t>Navneet</t>
@@ -6008,7 +6006,7 @@
       </c>
       <c r="H89" s="7" t="inlineStr">
         <is>
-          <t>EP Profile -&gt; Intervention Logs reflects every Activity Logger entry</t>
+          <t>Each framework status auto-updates on EP dashboard per activity completion</t>
         </is>
       </c>
       <c r="I89" s="7" t="inlineStr">
@@ -6022,127 +6020,129 @@
         </is>
       </c>
       <c r="K89" s="8" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="L89" s="8" t="n">
-        <v>46179</v>
+        <v>46182</v>
       </c>
       <c r="M89" s="7" t="n"/>
       <c r="N89" s="7" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="7" t="n">
+      <c r="A90" s="9" t="n">
         <v>89</v>
       </c>
-      <c r="B90" s="7" t="inlineStr">
-        <is>
-          <t>9.8</t>
-        </is>
-      </c>
-      <c r="C90" s="7" t="inlineStr">
-        <is>
-          <t>Framework completion tracking (Not Started -&gt; Completed -&gt; xN)</t>
-        </is>
-      </c>
-      <c r="D90" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="E90" s="7" t="inlineStr">
-        <is>
-          <t>Backend Dev</t>
-        </is>
-      </c>
-      <c r="F90" s="7" t="inlineStr">
-        <is>
-          <t>9.7</t>
-        </is>
-      </c>
-      <c r="G90" s="7" t="inlineStr">
-        <is>
-          <t>Navneet</t>
-        </is>
-      </c>
-      <c r="H90" s="7" t="inlineStr">
-        <is>
-          <t>Each framework status auto-updates on EP dashboard per activity completion</t>
-        </is>
-      </c>
-      <c r="I90" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J90" s="7" t="inlineStr">
+      <c r="B90" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C90" s="9" t="inlineStr">
+        <is>
+          <t>Landscape Dashboard</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="E90" s="9" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="F90" s="9" t="inlineStr">
+        <is>
+          <t>4,8</t>
+        </is>
+      </c>
+      <c r="G90" s="9" t="inlineStr">
+        <is>
+          <t>Navneet</t>
+        </is>
+      </c>
+      <c r="H90" s="9" t="inlineStr">
+        <is>
+          <t>Entrepreneurial Landscape Map with 6 filters + clustering + popup + village pins</t>
+        </is>
+      </c>
+      <c r="I90" s="9" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="J90" s="9" t="inlineStr">
         <is>
           <t>UAT-2</t>
         </is>
       </c>
-      <c r="K90" s="8" t="n">
-        <v>46176</v>
-      </c>
-      <c r="L90" s="8" t="n">
+      <c r="K90" s="10" t="n">
+        <v>46122</v>
+      </c>
+      <c r="L90" s="10" t="n">
         <v>46182</v>
       </c>
-      <c r="M90" s="7" t="n"/>
-      <c r="N90" s="7" t="n"/>
+      <c r="M90" s="10" t="n">
+        <v>46122</v>
+      </c>
+      <c r="N90" s="9" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="9" t="n">
+      <c r="A91" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="B91" s="9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C91" s="9" t="inlineStr">
-        <is>
-          <t>Landscape Dashboard</t>
-        </is>
-      </c>
-      <c r="D91" s="9" t="n">
-        <v>60</v>
-      </c>
-      <c r="E91" s="9" t="inlineStr">
-        <is>
-          <t>Developer</t>
-        </is>
-      </c>
-      <c r="F91" s="9" t="inlineStr">
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>Vue: Entrepreneurial Landscape Map (6 filters + clustering + popup)</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>Frontend Dev</t>
+        </is>
+      </c>
+      <c r="F91" s="7" t="inlineStr">
         <is>
           <t>4,8</t>
         </is>
       </c>
-      <c r="G91" s="9" t="inlineStr">
-        <is>
-          <t>Navneet</t>
-        </is>
-      </c>
-      <c r="H91" s="9" t="inlineStr">
-        <is>
-          <t>Entrepreneurial Landscape Map with 6 filters + clustering + popup + village pins</t>
-        </is>
-      </c>
-      <c r="I91" s="9" t="inlineStr">
+      <c r="G91" s="7" t="inlineStr">
+        <is>
+          <t>Navneet</t>
+        </is>
+      </c>
+      <c r="H91" s="7" t="inlineStr">
+        <is>
+          <t>Map renders all EPs as pins; 6-filter narrowing live; cluster on zoom-out</t>
+        </is>
+      </c>
+      <c r="I91" s="7" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="J91" s="9" t="inlineStr">
+      <c r="J91" s="7" t="inlineStr">
         <is>
           <t>UAT-2</t>
         </is>
       </c>
-      <c r="K91" s="10" t="n">
+      <c r="K91" s="8" t="n">
         <v>46122</v>
       </c>
-      <c r="L91" s="10" t="n">
-        <v>46182</v>
-      </c>
-      <c r="M91" s="10" t="n">
+      <c r="L91" s="8" t="n">
+        <v>46178</v>
+      </c>
+      <c r="M91" s="8" t="n">
         <v>46122</v>
       </c>
-      <c r="N91" s="9" t="n"/>
+      <c r="N91" s="7" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n">
@@ -6150,173 +6150,171 @@
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>Vue: Entrepreneurial Landscape Map (6 filters + clustering + popup)</t>
+          <t>Village Survey geo-pin overlay on Landscape Map</t>
         </is>
       </c>
       <c r="D92" s="7" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
+          <t>Backend Dev</t>
+        </is>
+      </c>
+      <c r="F92" s="7" t="inlineStr">
+        <is>
+          <t>8.4,10.1</t>
+        </is>
+      </c>
+      <c r="G92" s="7" t="inlineStr">
+        <is>
+          <t>Navneet</t>
+        </is>
+      </c>
+      <c r="H92" s="7" t="inlineStr">
+        <is>
+          <t>Village pins shown alongside EP pins with distinct icon</t>
+        </is>
+      </c>
+      <c r="I92" s="7" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J92" s="7" t="inlineStr">
+        <is>
+          <t>UAT-2</t>
+        </is>
+      </c>
+      <c r="K92" s="8" t="n">
+        <v>46175</v>
+      </c>
+      <c r="L92" s="8" t="n">
+        <v>46182</v>
+      </c>
+      <c r="M92" s="7" t="n"/>
+      <c r="N92" s="7" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="9" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C93" s="9" t="inlineStr">
+        <is>
+          <t>Milestone &amp; Activity Tracker</t>
+        </is>
+      </c>
+      <c r="D93" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="E93" s="9" t="inlineStr">
+        <is>
+          <t>Developer / Tech Lead</t>
+        </is>
+      </c>
+      <c r="F93" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G93" s="9" t="inlineStr">
+        <is>
+          <t>Navneet</t>
+        </is>
+      </c>
+      <c r="H93" s="9" t="inlineStr">
+        <is>
+          <t>Progress Matrix workspace with Overview/Activities/Timeline/RACI tabs [Bug 55 P1: dashboard non-functional, REGRESSED in UAT-1]</t>
+        </is>
+      </c>
+      <c r="I93" s="9" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="J93" s="9" t="inlineStr">
+        <is>
+          <t>UAT-2</t>
+        </is>
+      </c>
+      <c r="K93" s="10" t="n">
+        <v>46113</v>
+      </c>
+      <c r="L93" s="10" t="n">
+        <v>46124</v>
+      </c>
+      <c r="M93" s="10" t="n">
+        <v>46113</v>
+      </c>
+      <c r="N93" s="9" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="7" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="inlineStr">
+        <is>
+          <t>Vue: Milestone Tracker dashboard (4 tabs + lollipop + Gantt)</t>
+        </is>
+      </c>
+      <c r="D94" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E94" s="7" t="inlineStr">
+        <is>
           <t>Frontend Dev</t>
         </is>
       </c>
-      <c r="F92" s="7" t="inlineStr">
-        <is>
-          <t>4,8</t>
-        </is>
-      </c>
-      <c r="G92" s="7" t="inlineStr">
-        <is>
-          <t>Navneet</t>
-        </is>
-      </c>
-      <c r="H92" s="7" t="inlineStr">
-        <is>
-          <t>Map renders all EPs as pins; 6-filter narrowing live; cluster on zoom-out</t>
-        </is>
-      </c>
-      <c r="I92" s="7" t="inlineStr">
+      <c r="F94" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G94" s="7" t="inlineStr">
+        <is>
+          <t>Navneet</t>
+        </is>
+      </c>
+      <c r="H94" s="7" t="inlineStr">
+        <is>
+          <t>UI built; but Bug 55 (P1): get_milestone_data ModuleNotFoundError -&gt; 'Error loading data' + 0 records for ALL roles</t>
+        </is>
+      </c>
+      <c r="I94" s="7" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="J92" s="7" t="inlineStr">
+      <c r="J94" s="7" t="inlineStr">
         <is>
           <t>UAT-2</t>
         </is>
       </c>
-      <c r="K92" s="8" t="n">
-        <v>46122</v>
-      </c>
-      <c r="L92" s="8" t="n">
-        <v>46178</v>
-      </c>
-      <c r="M92" s="8" t="n">
-        <v>46122</v>
-      </c>
-      <c r="N92" s="7" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="7" t="n">
-        <v>92</v>
-      </c>
-      <c r="B93" s="7" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
-      </c>
-      <c r="C93" s="7" t="inlineStr">
-        <is>
-          <t>Village Survey geo-pin overlay on Landscape Map</t>
-        </is>
-      </c>
-      <c r="D93" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="E93" s="7" t="inlineStr">
-        <is>
-          <t>Backend Dev</t>
-        </is>
-      </c>
-      <c r="F93" s="7" t="inlineStr">
-        <is>
-          <t>8.4,10.1</t>
-        </is>
-      </c>
-      <c r="G93" s="7" t="inlineStr">
-        <is>
-          <t>Navneet</t>
-        </is>
-      </c>
-      <c r="H93" s="7" t="inlineStr">
-        <is>
-          <t>Village pins shown alongside EP pins with distinct icon</t>
-        </is>
-      </c>
-      <c r="I93" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J93" s="7" t="inlineStr">
-        <is>
-          <t>UAT-2</t>
-        </is>
-      </c>
-      <c r="K93" s="8" t="n">
-        <v>46175</v>
-      </c>
-      <c r="L93" s="8" t="n">
-        <v>46182</v>
-      </c>
-      <c r="M93" s="7" t="n"/>
-      <c r="N93" s="7" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="5" t="n">
-        <v>93</v>
-      </c>
-      <c r="B94" s="5" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C94" s="5" t="inlineStr">
-        <is>
-          <t>Milestone &amp; Activity Tracker</t>
-        </is>
-      </c>
-      <c r="D94" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="E94" s="5" t="inlineStr">
-        <is>
-          <t>Developer / Tech Lead</t>
-        </is>
-      </c>
-      <c r="F94" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G94" s="5" t="inlineStr">
-        <is>
-          <t>Navneet</t>
-        </is>
-      </c>
-      <c r="H94" s="5" t="inlineStr">
-        <is>
-          <t>Progress Matrix workspace with Overview/Activities/Timeline/RACI tabs</t>
-        </is>
-      </c>
-      <c r="I94" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="J94" s="5" t="inlineStr">
-        <is>
-          <t>UAT-2</t>
-        </is>
-      </c>
-      <c r="K94" s="6" t="n">
+      <c r="K94" s="8" t="n">
         <v>46113</v>
       </c>
-      <c r="L94" s="6" t="n">
-        <v>46124</v>
-      </c>
-      <c r="M94" s="6" t="n">
+      <c r="L94" s="8" t="n">
+        <v>46120</v>
+      </c>
+      <c r="M94" s="8" t="n">
         <v>46113</v>
       </c>
-      <c r="N94" s="6" t="n">
-        <v>46124</v>
-      </c>
+      <c r="N94" s="7" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="7" t="n">
@@ -6324,35 +6322,35 @@
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>Workspace + Web Page + CHB deployment (Progress Matrix)</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>Tech Lead</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
           <t>11.1</t>
         </is>
       </c>
-      <c r="C95" s="7" t="inlineStr">
-        <is>
-          <t>Vue: Milestone Tracker dashboard (4 tabs + lollipop + Gantt)</t>
-        </is>
-      </c>
-      <c r="D95" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="E95" s="7" t="inlineStr">
-        <is>
-          <t>Frontend Dev</t>
-        </is>
-      </c>
-      <c r="F95" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="G95" s="7" t="inlineStr">
         <is>
-          <t>Navneet</t>
+          <t>Bhushan</t>
         </is>
       </c>
       <c r="H95" s="7" t="inlineStr">
         <is>
-          <t>MilestoneTrackerDashboard.vue + 8 sub-components live; lollipop + Gantt render</t>
+          <t>/prime-rural-milestone-tracker live; Progress Matrix workspace seeded</t>
         </is>
       </c>
       <c r="I95" s="7" t="inlineStr">
@@ -6366,16 +6364,16 @@
         </is>
       </c>
       <c r="K95" s="8" t="n">
-        <v>46113</v>
+        <v>46121</v>
       </c>
       <c r="L95" s="8" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="M95" s="8" t="n">
-        <v>46113</v>
+        <v>46121</v>
       </c>
       <c r="N95" s="8" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
     </row>
     <row r="96">
@@ -6384,40 +6382,40 @@
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
+          <t>11.3</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="inlineStr">
+        <is>
+          <t>Milestone Master + Milestone Activity records populated (26 + 85)</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>PM</t>
+        </is>
+      </c>
+      <c r="F96" s="7" t="inlineStr">
+        <is>
           <t>11.2</t>
         </is>
       </c>
-      <c r="C96" s="7" t="inlineStr">
-        <is>
-          <t>Workspace + Web Page + CHB deployment (Progress Matrix)</t>
-        </is>
-      </c>
-      <c r="D96" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E96" s="7" t="inlineStr">
-        <is>
-          <t>Tech Lead</t>
-        </is>
-      </c>
-      <c r="F96" s="7" t="inlineStr">
-        <is>
-          <t>11.1</t>
-        </is>
-      </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>Bhushan</t>
+          <t>Samarth</t>
         </is>
       </c>
       <c r="H96" s="7" t="inlineStr">
         <is>
-          <t>/prime-rural-milestone-tracker live; Progress Matrix workspace seeded</t>
+          <t>26 milestones loaded; the 85 activities were lost in the Bug-55 regression - needs reseed</t>
         </is>
       </c>
       <c r="I96" s="7" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="J96" s="7" t="inlineStr">
@@ -6426,123 +6424,107 @@
         </is>
       </c>
       <c r="K96" s="8" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="L96" s="8" t="n">
-        <v>46121</v>
+        <v>46124</v>
       </c>
       <c r="M96" s="8" t="n">
-        <v>46121</v>
-      </c>
-      <c r="N96" s="8" t="n">
-        <v>46121</v>
-      </c>
+        <v>46122</v>
+      </c>
+      <c r="N96" s="7" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="7" t="n">
+      <c r="A97" s="11" t="n">
         <v>96</v>
       </c>
-      <c r="B97" s="7" t="inlineStr">
-        <is>
-          <t>11.3</t>
-        </is>
-      </c>
-      <c r="C97" s="7" t="inlineStr">
-        <is>
-          <t>Milestone Master + Milestone Activity records populated (26 + 85)</t>
-        </is>
-      </c>
-      <c r="D97" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E97" s="7" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="F97" s="7" t="inlineStr">
-        <is>
-          <t>11.2</t>
-        </is>
-      </c>
-      <c r="G97" s="7" t="inlineStr">
+      <c r="B97" s="11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C97" s="11" t="inlineStr">
+        <is>
+          <t>Intervention Dashboard &amp; KPI Form</t>
+        </is>
+      </c>
+      <c r="D97" s="11" t="n"/>
+      <c r="E97" s="11" t="inlineStr">
+        <is>
+          <t>Developer + PM + Client</t>
+        </is>
+      </c>
+      <c r="F97" s="11" t="inlineStr"/>
+      <c r="G97" s="11" t="inlineStr">
+        <is>
+          <t>Navneet</t>
+        </is>
+      </c>
+      <c r="H97" s="11" t="inlineStr">
+        <is>
+          <t>Requirement finalisation needed - KPI form spec pending from client (post 20-May meeting)</t>
+        </is>
+      </c>
+      <c r="I97" s="11" t="inlineStr">
+        <is>
+          <t>Pending Requirements</t>
+        </is>
+      </c>
+      <c r="J97" s="11" t="inlineStr">
+        <is>
+          <t>UAT-3</t>
+        </is>
+      </c>
+      <c r="K97" s="11" t="n"/>
+      <c r="L97" s="11" t="n"/>
+      <c r="M97" s="11" t="n"/>
+      <c r="N97" s="11" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="7" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="7" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="inlineStr">
+        <is>
+          <t>KPI form spec gathering from client (Minha + Alem)</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="n"/>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>PM + Client</t>
+        </is>
+      </c>
+      <c r="F98" s="7" t="inlineStr"/>
+      <c r="G98" s="7" t="inlineStr">
         <is>
           <t>Samarth</t>
         </is>
       </c>
-      <c r="H97" s="7" t="inlineStr">
-        <is>
-          <t>26 milestones + 85 activities loaded from RACI sheet</t>
-        </is>
-      </c>
-      <c r="I97" s="7" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="J97" s="7" t="inlineStr">
-        <is>
-          <t>UAT-2</t>
-        </is>
-      </c>
-      <c r="K97" s="8" t="n">
-        <v>46122</v>
-      </c>
-      <c r="L97" s="8" t="n">
-        <v>46124</v>
-      </c>
-      <c r="M97" s="8" t="n">
-        <v>46122</v>
-      </c>
-      <c r="N97" s="8" t="n">
-        <v>46124</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="11" t="n">
-        <v>97</v>
-      </c>
-      <c r="B98" s="11" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C98" s="11" t="inlineStr">
-        <is>
-          <t>Intervention Dashboard &amp; KPI Form</t>
-        </is>
-      </c>
-      <c r="D98" s="11" t="n"/>
-      <c r="E98" s="11" t="inlineStr">
-        <is>
-          <t>Developer + PM + Client</t>
-        </is>
-      </c>
-      <c r="F98" s="11" t="inlineStr"/>
-      <c r="G98" s="11" t="inlineStr">
-        <is>
-          <t>Navneet</t>
-        </is>
-      </c>
-      <c r="H98" s="11" t="inlineStr">
-        <is>
-          <t>Requirement finalisation needed - KPI form spec pending from client (post 20-May meeting)</t>
-        </is>
-      </c>
-      <c r="I98" s="11" t="inlineStr">
+      <c r="H98" s="7" t="inlineStr">
+        <is>
+          <t>KPI list + form fields + dashboard wireframe signed off by MBMA</t>
+        </is>
+      </c>
+      <c r="I98" s="7" t="inlineStr">
         <is>
           <t>Pending Requirements</t>
         </is>
       </c>
-      <c r="J98" s="11" t="inlineStr">
+      <c r="J98" s="7" t="inlineStr">
         <is>
           <t>UAT-3</t>
         </is>
       </c>
-      <c r="K98" s="11" t="n"/>
-      <c r="L98" s="11" t="n"/>
-      <c r="M98" s="11" t="n"/>
-      <c r="N98" s="11" t="n"/>
+      <c r="K98" s="7" t="n"/>
+      <c r="L98" s="7" t="n"/>
+      <c r="M98" s="7" t="n"/>
+      <c r="N98" s="7" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="7" t="n">
@@ -6550,29 +6532,33 @@
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>KPI form spec gathering from client (Minha + Alem)</t>
+          <t>Intervention Dashboard rebuild (KPIs + Sankey + drill-down)</t>
         </is>
       </c>
       <c r="D99" s="7" t="n"/>
       <c r="E99" s="7" t="inlineStr">
         <is>
-          <t>PM + Client</t>
-        </is>
-      </c>
-      <c r="F99" s="7" t="inlineStr"/>
+          <t>Frontend Dev</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
       <c r="G99" s="7" t="inlineStr">
         <is>
-          <t>Samarth</t>
+          <t>Navneet</t>
         </is>
       </c>
       <c r="H99" s="7" t="inlineStr">
         <is>
-          <t>KPI list + form fields + dashboard wireframe signed off by MBMA</t>
+          <t>Dashboard reflects signed-off KPIs with live data + drill-down</t>
         </is>
       </c>
       <c r="I99" s="7" t="inlineStr">
@@ -6596,25 +6582,23 @@
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>Intervention Dashboard rebuild (KPIs + Sankey + drill-down)</t>
-        </is>
-      </c>
-      <c r="D100" s="7" t="n"/>
+          <t>Sankey Flow component (already built; needs KPI wiring)</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="n">
+        <v>7</v>
+      </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
           <t>Frontend Dev</t>
         </is>
       </c>
-      <c r="F100" s="7" t="inlineStr">
-        <is>
-          <t>12.1</t>
-        </is>
-      </c>
+      <c r="F100" s="7" t="inlineStr"/>
       <c r="G100" s="7" t="inlineStr">
         <is>
           <t>Navneet</t>
@@ -6622,125 +6606,123 @@
       </c>
       <c r="H100" s="7" t="inlineStr">
         <is>
-          <t>Dashboard reflects signed-off KPIs with live data + drill-down</t>
+          <t>SankeyFlow.vue renders MET -&gt; Incubated/Supported -&gt; sectors</t>
         </is>
       </c>
       <c r="I100" s="7" t="inlineStr">
         <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="J100" s="7" t="inlineStr">
+        <is>
+          <t>Pre-UAT</t>
+        </is>
+      </c>
+      <c r="K100" s="8" t="n">
+        <v>46123</v>
+      </c>
+      <c r="L100" s="8" t="n">
+        <v>46129</v>
+      </c>
+      <c r="M100" s="8" t="n">
+        <v>46123</v>
+      </c>
+      <c r="N100" s="8" t="n">
+        <v>46129</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C101" s="11" t="inlineStr">
+        <is>
+          <t>Apoorva AI Integration</t>
+        </is>
+      </c>
+      <c r="D101" s="11" t="n"/>
+      <c r="E101" s="11" t="inlineStr">
+        <is>
+          <t>Developer + Client</t>
+        </is>
+      </c>
+      <c r="F101" s="11" t="inlineStr"/>
+      <c r="G101" s="11" t="inlineStr">
+        <is>
+          <t>Navneet</t>
+        </is>
+      </c>
+      <c r="H101" s="11" t="inlineStr">
+        <is>
+          <t>Requirement finalisation needed - integration spec pending from Apoorva AI team</t>
+        </is>
+      </c>
+      <c r="I101" s="11" t="inlineStr">
+        <is>
           <t>Pending Requirements</t>
         </is>
       </c>
-      <c r="J100" s="7" t="inlineStr">
+      <c r="J101" s="11" t="inlineStr">
         <is>
           <t>UAT-3</t>
         </is>
       </c>
-      <c r="K100" s="7" t="n"/>
-      <c r="L100" s="7" t="n"/>
-      <c r="M100" s="7" t="n"/>
-      <c r="N100" s="7" t="n"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="B101" s="7" t="inlineStr">
-        <is>
-          <t>12.3</t>
-        </is>
-      </c>
-      <c r="C101" s="7" t="inlineStr">
-        <is>
-          <t>Sankey Flow component (already built; needs KPI wiring)</t>
-        </is>
-      </c>
-      <c r="D101" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="E101" s="7" t="inlineStr">
-        <is>
-          <t>Frontend Dev</t>
-        </is>
-      </c>
-      <c r="F101" s="7" t="inlineStr"/>
-      <c r="G101" s="7" t="inlineStr">
-        <is>
-          <t>Navneet</t>
-        </is>
-      </c>
-      <c r="H101" s="7" t="inlineStr">
-        <is>
-          <t>SankeyFlow.vue renders MET -&gt; Incubated/Supported -&gt; sectors</t>
-        </is>
-      </c>
-      <c r="I101" s="7" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="J101" s="7" t="inlineStr">
-        <is>
-          <t>Pre-UAT</t>
-        </is>
-      </c>
-      <c r="K101" s="8" t="n">
-        <v>46123</v>
-      </c>
-      <c r="L101" s="8" t="n">
-        <v>46129</v>
-      </c>
-      <c r="M101" s="8" t="n">
-        <v>46123</v>
-      </c>
-      <c r="N101" s="8" t="n">
-        <v>46129</v>
-      </c>
+      <c r="K101" s="11" t="n"/>
+      <c r="L101" s="11" t="n"/>
+      <c r="M101" s="11" t="n"/>
+      <c r="N101" s="11" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="11" t="n">
+      <c r="A102" s="7" t="n">
         <v>101</v>
       </c>
-      <c r="B102" s="11" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="C102" s="11" t="inlineStr">
-        <is>
-          <t>Apoorva AI Integration</t>
-        </is>
-      </c>
-      <c r="D102" s="11" t="n"/>
-      <c r="E102" s="11" t="inlineStr">
-        <is>
-          <t>Developer + Client</t>
-        </is>
-      </c>
-      <c r="F102" s="11" t="inlineStr"/>
-      <c r="G102" s="11" t="inlineStr">
-        <is>
-          <t>Navneet</t>
-        </is>
-      </c>
-      <c r="H102" s="11" t="inlineStr">
-        <is>
-          <t>Requirement finalisation needed - integration spec pending from Apoorva AI team</t>
-        </is>
-      </c>
-      <c r="I102" s="11" t="inlineStr">
+      <c r="B102" s="7" t="inlineStr">
+        <is>
+          <t>13.1</t>
+        </is>
+      </c>
+      <c r="C102" s="7" t="inlineStr">
+        <is>
+          <t>Integration spec with Apoorva AI team (endpoints + auth + context model)</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="n"/>
+      <c r="E102" s="7" t="inlineStr">
+        <is>
+          <t>PM + Client</t>
+        </is>
+      </c>
+      <c r="F102" s="7" t="inlineStr"/>
+      <c r="G102" s="7" t="inlineStr">
+        <is>
+          <t>Samarth</t>
+        </is>
+      </c>
+      <c r="H102" s="7" t="inlineStr">
+        <is>
+          <t>API contract signed; auth + rate limits agreed</t>
+        </is>
+      </c>
+      <c r="I102" s="7" t="inlineStr">
         <is>
           <t>Pending Requirements</t>
         </is>
       </c>
-      <c r="J102" s="11" t="inlineStr">
+      <c r="J102" s="7" t="inlineStr">
         <is>
           <t>UAT-3</t>
         </is>
       </c>
-      <c r="K102" s="11" t="n"/>
-      <c r="L102" s="11" t="n"/>
-      <c r="M102" s="11" t="n"/>
-      <c r="N102" s="11" t="n"/>
+      <c r="K102" s="7" t="n"/>
+      <c r="L102" s="7" t="n"/>
+      <c r="M102" s="7" t="n"/>
+      <c r="N102" s="7" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="7" t="n">
@@ -6748,29 +6730,33 @@
       </c>
       <c r="B103" s="7" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>Integration spec with Apoorva AI team (endpoints + auth + context model)</t>
+          <t>Chatbot widget on portal (entrepreneur-facing)</t>
         </is>
       </c>
       <c r="D103" s="7" t="n"/>
       <c r="E103" s="7" t="inlineStr">
         <is>
-          <t>PM + Client</t>
-        </is>
-      </c>
-      <c r="F103" s="7" t="inlineStr"/>
+          <t>Frontend Dev</t>
+        </is>
+      </c>
+      <c r="F103" s="7" t="inlineStr">
+        <is>
+          <t>13.1</t>
+        </is>
+      </c>
       <c r="G103" s="7" t="inlineStr">
         <is>
-          <t>Samarth</t>
+          <t>Navneet</t>
         </is>
       </c>
       <c r="H103" s="7" t="inlineStr">
         <is>
-          <t>API contract signed; auth + rate limits agreed</t>
+          <t>Widget docks on portal; sends + receives messages</t>
         </is>
       </c>
       <c r="I103" s="7" t="inlineStr">
@@ -6794,18 +6780,18 @@
       </c>
       <c r="B104" s="7" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>Chatbot widget on portal (entrepreneur-facing)</t>
+          <t>AI Generate: Label Storyline (in Labels Required tab)</t>
         </is>
       </c>
       <c r="D104" s="7" t="n"/>
       <c r="E104" s="7" t="inlineStr">
         <is>
-          <t>Frontend Dev</t>
+          <t>Backend Dev</t>
         </is>
       </c>
       <c r="F104" s="7" t="inlineStr">
@@ -6820,7 +6806,7 @@
       </c>
       <c r="H104" s="7" t="inlineStr">
         <is>
-          <t>Widget docks on portal; sends + receives messages</t>
+          <t>Button on Label form generates storyline draft via Apoorva</t>
         </is>
       </c>
       <c r="I104" s="7" t="inlineStr">
@@ -6844,12 +6830,12 @@
       </c>
       <c r="B105" s="7" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>AI Generate: Label Storyline (in Labels Required tab)</t>
+          <t>AI Generate: Brochure Storyline (in Brochure form)</t>
         </is>
       </c>
       <c r="D105" s="7" t="n"/>
@@ -6870,7 +6856,7 @@
       </c>
       <c r="H105" s="7" t="inlineStr">
         <is>
-          <t>Button on Label form generates storyline draft via Apoorva</t>
+          <t>Button on Brochure form generates storyline draft via Apoorva</t>
         </is>
       </c>
       <c r="I105" s="7" t="inlineStr">
@@ -6894,12 +6880,12 @@
       </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>AI Generate: Brochure Storyline (in Brochure form)</t>
+          <t>Context-aware responses (pass entrepreneur data to model)</t>
         </is>
       </c>
       <c r="D106" s="7" t="n"/>
@@ -6920,7 +6906,7 @@
       </c>
       <c r="H106" s="7" t="inlineStr">
         <is>
-          <t>Button on Brochure form generates storyline draft via Apoorva</t>
+          <t>Chatbot answers reference the current entrepreneur's data</t>
         </is>
       </c>
       <c r="I106" s="7" t="inlineStr">
@@ -6939,100 +6925,96 @@
       <c r="N106" s="7" t="n"/>
     </row>
     <row r="107">
-      <c r="A107" s="7" t="n">
+      <c r="A107" s="11" t="n">
         <v>106</v>
       </c>
-      <c r="B107" s="7" t="inlineStr">
-        <is>
-          <t>13.5</t>
-        </is>
-      </c>
-      <c r="C107" s="7" t="inlineStr">
-        <is>
-          <t>Context-aware responses (pass entrepreneur data to model)</t>
-        </is>
-      </c>
-      <c r="D107" s="7" t="n"/>
-      <c r="E107" s="7" t="inlineStr">
-        <is>
-          <t>Backend Dev</t>
-        </is>
-      </c>
-      <c r="F107" s="7" t="inlineStr">
-        <is>
-          <t>13.1</t>
-        </is>
-      </c>
-      <c r="G107" s="7" t="inlineStr">
-        <is>
-          <t>Navneet</t>
-        </is>
-      </c>
-      <c r="H107" s="7" t="inlineStr">
-        <is>
-          <t>Chatbot answers reference the current entrepreneur's data</t>
-        </is>
-      </c>
-      <c r="I107" s="7" t="inlineStr">
+      <c r="B107" s="11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C107" s="11" t="inlineStr">
+        <is>
+          <t>Claude-based Chatbot</t>
+        </is>
+      </c>
+      <c r="D107" s="11" t="n"/>
+      <c r="E107" s="11" t="inlineStr">
+        <is>
+          <t>Developer + Client</t>
+        </is>
+      </c>
+      <c r="F107" s="11" t="inlineStr"/>
+      <c r="G107" s="11" t="inlineStr">
+        <is>
+          <t>Navneet</t>
+        </is>
+      </c>
+      <c r="H107" s="11" t="inlineStr">
+        <is>
+          <t>Requirement finalisation needed - scope of Claude vs Apoorva to be agreed</t>
+        </is>
+      </c>
+      <c r="I107" s="11" t="inlineStr">
         <is>
           <t>Pending Requirements</t>
         </is>
       </c>
-      <c r="J107" s="7" t="inlineStr">
+      <c r="J107" s="11" t="inlineStr">
         <is>
           <t>UAT-3</t>
         </is>
       </c>
-      <c r="K107" s="7" t="n"/>
-      <c r="L107" s="7" t="n"/>
-      <c r="M107" s="7" t="n"/>
-      <c r="N107" s="7" t="n"/>
+      <c r="K107" s="11" t="n"/>
+      <c r="L107" s="11" t="n"/>
+      <c r="M107" s="11" t="n"/>
+      <c r="N107" s="11" t="n"/>
     </row>
     <row r="108">
-      <c r="A108" s="11" t="n">
+      <c r="A108" s="7" t="n">
         <v>107</v>
       </c>
-      <c r="B108" s="11" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="C108" s="11" t="inlineStr">
-        <is>
-          <t>Claude-based Chatbot</t>
-        </is>
-      </c>
-      <c r="D108" s="11" t="n"/>
-      <c r="E108" s="11" t="inlineStr">
-        <is>
-          <t>Developer + Client</t>
-        </is>
-      </c>
-      <c r="F108" s="11" t="inlineStr"/>
-      <c r="G108" s="11" t="inlineStr">
-        <is>
-          <t>Navneet</t>
-        </is>
-      </c>
-      <c r="H108" s="11" t="inlineStr">
-        <is>
-          <t>Requirement finalisation needed - scope of Claude vs Apoorva to be agreed</t>
-        </is>
-      </c>
-      <c r="I108" s="11" t="inlineStr">
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>14.1</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="inlineStr">
+        <is>
+          <t>Claude integration spec (MCP scope, tool list, auth model)</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="n"/>
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t>PM + Client</t>
+        </is>
+      </c>
+      <c r="F108" s="7" t="inlineStr"/>
+      <c r="G108" s="7" t="inlineStr">
+        <is>
+          <t>Samarth</t>
+        </is>
+      </c>
+      <c r="H108" s="7" t="inlineStr">
+        <is>
+          <t>Tool list + auth model + which user roles get access agreed</t>
+        </is>
+      </c>
+      <c r="I108" s="7" t="inlineStr">
         <is>
           <t>Pending Requirements</t>
         </is>
       </c>
-      <c r="J108" s="11" t="inlineStr">
+      <c r="J108" s="7" t="inlineStr">
         <is>
           <t>UAT-3</t>
         </is>
       </c>
-      <c r="K108" s="11" t="n"/>
-      <c r="L108" s="11" t="n"/>
-      <c r="M108" s="11" t="n"/>
-      <c r="N108" s="11" t="n"/>
+      <c r="K108" s="7" t="n"/>
+      <c r="L108" s="7" t="n"/>
+      <c r="M108" s="7" t="n"/>
+      <c r="N108" s="7" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="7" t="n">
@@ -7040,29 +7022,33 @@
       </c>
       <c r="B109" s="7" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>Claude integration spec (MCP scope, tool list, auth model)</t>
+          <t>Internal-team chatbot widget (Core Team IT / PM use)</t>
         </is>
       </c>
       <c r="D109" s="7" t="n"/>
       <c r="E109" s="7" t="inlineStr">
         <is>
-          <t>PM + Client</t>
-        </is>
-      </c>
-      <c r="F109" s="7" t="inlineStr"/>
+          <t>Frontend Dev</t>
+        </is>
+      </c>
+      <c r="F109" s="7" t="inlineStr">
+        <is>
+          <t>14.1</t>
+        </is>
+      </c>
       <c r="G109" s="7" t="inlineStr">
         <is>
-          <t>Samarth</t>
+          <t>Navneet</t>
         </is>
       </c>
       <c r="H109" s="7" t="inlineStr">
         <is>
-          <t>Tool list + auth model + which user roles get access agreed</t>
+          <t>Chatbot panel for internal users with MCP-powered queries</t>
         </is>
       </c>
       <c r="I109" s="7" t="inlineStr">
@@ -7086,18 +7072,18 @@
       </c>
       <c r="B110" s="7" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>Internal-team chatbot widget (Core Team IT / PM use)</t>
+          <t>Tool integration: entrepreneur queries, status updates, dashboard pulls</t>
         </is>
       </c>
       <c r="D110" s="7" t="n"/>
       <c r="E110" s="7" t="inlineStr">
         <is>
-          <t>Frontend Dev</t>
+          <t>Backend Dev</t>
         </is>
       </c>
       <c r="F110" s="7" t="inlineStr">
@@ -7112,7 +7098,7 @@
       </c>
       <c r="H110" s="7" t="inlineStr">
         <is>
-          <t>Chatbot panel for internal users with MCP-powered queries</t>
+          <t>MCP server exposes write tools beyond current read-only set</t>
         </is>
       </c>
       <c r="I110" s="7" t="inlineStr">
@@ -7131,112 +7117,120 @@
       <c r="N110" s="7" t="n"/>
     </row>
     <row r="111">
-      <c r="A111" s="7" t="n">
+      <c r="A111" s="9" t="n">
         <v>110</v>
       </c>
-      <c r="B111" s="7" t="inlineStr">
-        <is>
-          <t>14.3</t>
-        </is>
-      </c>
-      <c r="C111" s="7" t="inlineStr">
-        <is>
-          <t>Tool integration: entrepreneur queries, status updates, dashboard pulls</t>
-        </is>
-      </c>
-      <c r="D111" s="7" t="n"/>
-      <c r="E111" s="7" t="inlineStr">
-        <is>
-          <t>Backend Dev</t>
-        </is>
-      </c>
-      <c r="F111" s="7" t="inlineStr">
-        <is>
-          <t>14.1</t>
-        </is>
-      </c>
-      <c r="G111" s="7" t="inlineStr">
-        <is>
-          <t>Navneet</t>
-        </is>
-      </c>
-      <c r="H111" s="7" t="inlineStr">
-        <is>
-          <t>MCP server exposes write tools beyond current read-only set</t>
-        </is>
-      </c>
-      <c r="I111" s="7" t="inlineStr">
-        <is>
-          <t>Pending Requirements</t>
-        </is>
-      </c>
-      <c r="J111" s="7" t="inlineStr">
-        <is>
-          <t>UAT-3</t>
-        </is>
-      </c>
-      <c r="K111" s="7" t="n"/>
-      <c r="L111" s="7" t="n"/>
-      <c r="M111" s="7" t="n"/>
-      <c r="N111" s="7" t="n"/>
+      <c r="B111" s="9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C111" s="9" t="inlineStr">
+        <is>
+          <t>QA, VAPT &amp; Performance</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="E111" s="9" t="inlineStr">
+        <is>
+          <t>Testing / DevOps / Tech Lead</t>
+        </is>
+      </c>
+      <c r="F111" s="9" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="G111" s="9" t="inlineStr">
+        <is>
+          <t>Chitranshi</t>
+        </is>
+      </c>
+      <c r="H111" s="9" t="inlineStr">
+        <is>
+          <t>All UAT cycles run; VAPT + load tests cleared before go-live</t>
+        </is>
+      </c>
+      <c r="I111" s="9" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="J111" s="9" t="inlineStr">
+        <is>
+          <t>UAT-1</t>
+        </is>
+      </c>
+      <c r="K111" s="10" t="n">
+        <v>46167</v>
+      </c>
+      <c r="L111" s="10" t="n">
+        <v>46206</v>
+      </c>
+      <c r="M111" s="10" t="n">
+        <v>46167</v>
+      </c>
+      <c r="N111" s="9" t="n"/>
     </row>
     <row r="112">
-      <c r="A112" s="9" t="n">
+      <c r="A112" s="7" t="n">
         <v>111</v>
       </c>
-      <c r="B112" s="9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="C112" s="9" t="inlineStr">
-        <is>
-          <t>QA, VAPT &amp; Performance</t>
-        </is>
-      </c>
-      <c r="D112" s="9" t="n">
-        <v>40</v>
-      </c>
-      <c r="E112" s="9" t="inlineStr">
-        <is>
-          <t>Testing / DevOps / Tech Lead</t>
-        </is>
-      </c>
-      <c r="F112" s="9" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="G112" s="9" t="inlineStr">
-        <is>
-          <t>Chitranshi</t>
-        </is>
-      </c>
-      <c r="H112" s="9" t="inlineStr">
-        <is>
-          <t>All UAT cycles run; VAPT + load tests cleared before go-live</t>
-        </is>
-      </c>
-      <c r="I112" s="9" t="inlineStr">
+      <c r="B112" s="7" t="inlineStr">
+        <is>
+          <t>15.1</t>
+        </is>
+      </c>
+      <c r="C112" s="7" t="inlineStr">
+        <is>
+          <t>UAT environment setup (separate from staging)</t>
+        </is>
+      </c>
+      <c r="D112" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E112" s="7" t="inlineStr">
+        <is>
+          <t>DevOps</t>
+        </is>
+      </c>
+      <c r="F112" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G112" s="7" t="inlineStr">
+        <is>
+          <t>Prakash</t>
+        </is>
+      </c>
+      <c r="H112" s="7" t="inlineStr">
+        <is>
+          <t>uat.prime-rural.dhwaniris.in live with prod-like data snapshot</t>
+        </is>
+      </c>
+      <c r="I112" s="7" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="J112" s="9" t="inlineStr">
+      <c r="J112" s="7" t="inlineStr">
         <is>
           <t>UAT-1</t>
         </is>
       </c>
-      <c r="K112" s="10" t="n">
+      <c r="K112" s="8" t="n">
         <v>46167</v>
       </c>
-      <c r="L112" s="10" t="n">
-        <v>46206</v>
-      </c>
-      <c r="M112" s="10" t="n">
+      <c r="L112" s="8" t="n">
+        <v>46170</v>
+      </c>
+      <c r="M112" s="8" t="n">
         <v>46167</v>
       </c>
-      <c r="N112" s="9" t="n"/>
+      <c r="N112" s="7" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="7" t="n">
@@ -7244,12 +7238,12 @@
       </c>
       <c r="B113" s="7" t="inlineStr">
         <is>
-          <t>15.1</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>UAT environment setup (separate from staging)</t>
+          <t>UAT-1 test scripts (User Mgmt + Masters + EP + Product + 27 frameworks + Activity Logger)</t>
         </is>
       </c>
       <c r="D113" s="7" t="n">
@@ -7257,27 +7251,27 @@
       </c>
       <c r="E113" s="7" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>QA Engineer</t>
         </is>
       </c>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15.1</t>
         </is>
       </c>
       <c r="G113" s="7" t="inlineStr">
         <is>
-          <t>Prakash</t>
+          <t>Chitranshi</t>
         </is>
       </c>
       <c r="H113" s="7" t="inlineStr">
         <is>
-          <t>uat.prime-rural.dhwaniris.in live with prod-like data snapshot</t>
+          <t>330 TDD cases documented + Playwright E2E suite committed; checklist live on GitHub Pages</t>
         </is>
       </c>
       <c r="I113" s="7" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="J113" s="7" t="inlineStr">
@@ -7286,15 +7280,17 @@
         </is>
       </c>
       <c r="K113" s="8" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="L113" s="8" t="n">
-        <v>46170</v>
+        <v>46180</v>
       </c>
       <c r="M113" s="8" t="n">
-        <v>46167</v>
-      </c>
-      <c r="N113" s="7" t="n"/>
+        <v>46168</v>
+      </c>
+      <c r="N113" s="8" t="n">
+        <v>46180</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="7" t="n">
@@ -7302,35 +7298,35 @@
       </c>
       <c r="B114" s="7" t="inlineStr">
         <is>
+          <t>15.3</t>
+        </is>
+      </c>
+      <c r="C114" s="7" t="inlineStr">
+        <is>
+          <t>UAT-1 internal dry run (E2E against staging)</t>
+        </is>
+      </c>
+      <c r="D114" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E114" s="7" t="inlineStr">
+        <is>
+          <t>QA + PM</t>
+        </is>
+      </c>
+      <c r="F114" s="7" t="inlineStr">
+        <is>
           <t>15.2</t>
         </is>
       </c>
-      <c r="C114" s="7" t="inlineStr">
-        <is>
-          <t>UAT-1 test scripts (User Mgmt + Masters + EP + Product + 27 frameworks + Activity Logger)</t>
-        </is>
-      </c>
-      <c r="D114" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E114" s="7" t="inlineStr">
-        <is>
-          <t>QA Engineer</t>
-        </is>
-      </c>
-      <c r="F114" s="7" t="inlineStr">
-        <is>
-          <t>15.1</t>
-        </is>
-      </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
-          <t>Chitranshi</t>
+          <t>Chitranshi / Samarth</t>
         </is>
       </c>
       <c r="H114" s="7" t="inlineStr">
         <is>
-          <t>Test scripts cover BRD E2E for UAT-1 scope; checklist signed off</t>
+          <t>E2E executed 7-8 Jun: 272 cases run (67 pass / 37 fail / 168 blocked), ~60 bugs logged; 3 P1 fixes pending</t>
         </is>
       </c>
       <c r="I114" s="7" t="inlineStr">
@@ -7344,13 +7340,13 @@
         </is>
       </c>
       <c r="K114" s="8" t="n">
-        <v>46168</v>
+        <v>46171</v>
       </c>
       <c r="L114" s="8" t="n">
-        <v>46170</v>
+        <v>46181</v>
       </c>
       <c r="M114" s="8" t="n">
-        <v>46168</v>
+        <v>46171</v>
       </c>
       <c r="N114" s="7" t="n"/>
     </row>
@@ -7360,12 +7356,12 @@
       </c>
       <c r="B115" s="7" t="inlineStr">
         <is>
-          <t>15.3</t>
+          <t>15.4</t>
         </is>
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>UAT-1 internal dry run</t>
+          <t>UAT-1 with client (MBMA team)</t>
         </is>
       </c>
       <c r="D115" s="7" t="n">
@@ -7373,22 +7369,22 @@
       </c>
       <c r="E115" s="7" t="inlineStr">
         <is>
-          <t>QA + PM</t>
+          <t>PM + Client</t>
         </is>
       </c>
       <c r="F115" s="7" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>15.3</t>
         </is>
       </c>
       <c r="G115" s="7" t="inlineStr">
         <is>
-          <t>Chitranshi / Samarth</t>
+          <t>Samarth</t>
         </is>
       </c>
       <c r="H115" s="7" t="inlineStr">
         <is>
-          <t>Critical bugs from dry run fixed before client UAT</t>
+          <t>Client signs off UAT-1 scope or files defects</t>
         </is>
       </c>
       <c r="I115" s="7" t="inlineStr">
@@ -7402,10 +7398,10 @@
         </is>
       </c>
       <c r="K115" s="8" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="L115" s="8" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="M115" s="7" t="n"/>
       <c r="N115" s="7" t="n"/>
@@ -7416,35 +7412,35 @@
       </c>
       <c r="B116" s="7" t="inlineStr">
         <is>
+          <t>15.5</t>
+        </is>
+      </c>
+      <c r="C116" s="7" t="inlineStr">
+        <is>
+          <t>UAT-1 bug fixing sprint</t>
+        </is>
+      </c>
+      <c r="D116" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E116" s="7" t="inlineStr">
+        <is>
+          <t>Tech Lead + Developer</t>
+        </is>
+      </c>
+      <c r="F116" s="7" t="inlineStr">
+        <is>
           <t>15.4</t>
         </is>
       </c>
-      <c r="C116" s="7" t="inlineStr">
-        <is>
-          <t>UAT-1 with client (MBMA team)</t>
-        </is>
-      </c>
-      <c r="D116" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E116" s="7" t="inlineStr">
-        <is>
-          <t>PM + Client</t>
-        </is>
-      </c>
-      <c r="F116" s="7" t="inlineStr">
-        <is>
-          <t>15.3</t>
-        </is>
-      </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
-          <t>Samarth</t>
+          <t>Bhushan</t>
         </is>
       </c>
       <c r="H116" s="7" t="inlineStr">
         <is>
-          <t>Client signs off UAT-1 scope or files defects</t>
+          <t>All UAT-1 P0/P1 defects fixed + redeployed</t>
         </is>
       </c>
       <c r="I116" s="7" t="inlineStr">
@@ -7458,10 +7454,10 @@
         </is>
       </c>
       <c r="K116" s="8" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="L116" s="8" t="n">
-        <v>46171</v>
+        <v>46178</v>
       </c>
       <c r="M116" s="7" t="n"/>
       <c r="N116" s="7" t="n"/>
@@ -7472,35 +7468,35 @@
       </c>
       <c r="B117" s="7" t="inlineStr">
         <is>
+          <t>15.6</t>
+        </is>
+      </c>
+      <c r="C117" s="7" t="inlineStr">
+        <is>
+          <t>UAT-2 test scripts (Research Notes + Village Survey + Landscape + Milestone Tracker)</t>
+        </is>
+      </c>
+      <c r="D117" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E117" s="7" t="inlineStr">
+        <is>
+          <t>QA Engineer</t>
+        </is>
+      </c>
+      <c r="F117" s="7" t="inlineStr">
+        <is>
           <t>15.5</t>
         </is>
       </c>
-      <c r="C117" s="7" t="inlineStr">
-        <is>
-          <t>UAT-1 bug fixing sprint</t>
-        </is>
-      </c>
-      <c r="D117" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="E117" s="7" t="inlineStr">
-        <is>
-          <t>Tech Lead + Developer</t>
-        </is>
-      </c>
-      <c r="F117" s="7" t="inlineStr">
-        <is>
-          <t>15.4</t>
-        </is>
-      </c>
       <c r="G117" s="7" t="inlineStr">
         <is>
-          <t>Bhushan</t>
+          <t>Chitranshi</t>
         </is>
       </c>
       <c r="H117" s="7" t="inlineStr">
         <is>
-          <t>All UAT-1 P0/P1 defects fixed + redeployed</t>
+          <t>Test scripts for UAT-2 scope signed off</t>
         </is>
       </c>
       <c r="I117" s="7" t="inlineStr">
@@ -7510,14 +7506,14 @@
       </c>
       <c r="J117" s="7" t="inlineStr">
         <is>
-          <t>UAT-1</t>
+          <t>UAT-2</t>
         </is>
       </c>
       <c r="K117" s="8" t="n">
-        <v>46172</v>
+        <v>46181</v>
       </c>
       <c r="L117" s="8" t="n">
-        <v>46178</v>
+        <v>46184</v>
       </c>
       <c r="M117" s="7" t="n"/>
       <c r="N117" s="7" t="n"/>
@@ -7528,35 +7524,35 @@
       </c>
       <c r="B118" s="7" t="inlineStr">
         <is>
+          <t>15.7</t>
+        </is>
+      </c>
+      <c r="C118" s="7" t="inlineStr">
+        <is>
+          <t>UAT-2 with client (MBMA team)</t>
+        </is>
+      </c>
+      <c r="D118" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E118" s="7" t="inlineStr">
+        <is>
+          <t>PM + Client</t>
+        </is>
+      </c>
+      <c r="F118" s="7" t="inlineStr">
+        <is>
           <t>15.6</t>
         </is>
       </c>
-      <c r="C118" s="7" t="inlineStr">
-        <is>
-          <t>UAT-2 test scripts (Research Notes + Village Survey + Landscape + Milestone Tracker)</t>
-        </is>
-      </c>
-      <c r="D118" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E118" s="7" t="inlineStr">
-        <is>
-          <t>QA Engineer</t>
-        </is>
-      </c>
-      <c r="F118" s="7" t="inlineStr">
-        <is>
-          <t>15.5</t>
-        </is>
-      </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
-          <t>Chitranshi</t>
+          <t>Samarth</t>
         </is>
       </c>
       <c r="H118" s="7" t="inlineStr">
         <is>
-          <t>Test scripts for UAT-2 scope signed off</t>
+          <t>Client signs off UAT-2 scope</t>
         </is>
       </c>
       <c r="I118" s="7" t="inlineStr">
@@ -7570,10 +7566,10 @@
         </is>
       </c>
       <c r="K118" s="8" t="n">
-        <v>46181</v>
+        <v>46185</v>
       </c>
       <c r="L118" s="8" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="M118" s="7" t="n"/>
       <c r="N118" s="7" t="n"/>
@@ -7584,35 +7580,35 @@
       </c>
       <c r="B119" s="7" t="inlineStr">
         <is>
+          <t>15.8</t>
+        </is>
+      </c>
+      <c r="C119" s="7" t="inlineStr">
+        <is>
+          <t>UAT-2 bug fixing sprint</t>
+        </is>
+      </c>
+      <c r="D119" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E119" s="7" t="inlineStr">
+        <is>
+          <t>Tech Lead + Developer</t>
+        </is>
+      </c>
+      <c r="F119" s="7" t="inlineStr">
+        <is>
           <t>15.7</t>
         </is>
       </c>
-      <c r="C119" s="7" t="inlineStr">
-        <is>
-          <t>UAT-2 with client (MBMA team)</t>
-        </is>
-      </c>
-      <c r="D119" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E119" s="7" t="inlineStr">
-        <is>
-          <t>PM + Client</t>
-        </is>
-      </c>
-      <c r="F119" s="7" t="inlineStr">
-        <is>
-          <t>15.6</t>
-        </is>
-      </c>
       <c r="G119" s="7" t="inlineStr">
         <is>
-          <t>Samarth</t>
+          <t>Bhushan</t>
         </is>
       </c>
       <c r="H119" s="7" t="inlineStr">
         <is>
-          <t>Client signs off UAT-2 scope</t>
+          <t>All UAT-2 P0/P1 defects fixed + redeployed</t>
         </is>
       </c>
       <c r="I119" s="7" t="inlineStr">
@@ -7626,10 +7622,10 @@
         </is>
       </c>
       <c r="K119" s="8" t="n">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="L119" s="8" t="n">
-        <v>46185</v>
+        <v>46192</v>
       </c>
       <c r="M119" s="7" t="n"/>
       <c r="N119" s="7" t="n"/>
@@ -7640,12 +7636,12 @@
       </c>
       <c r="B120" s="7" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="C120" s="7" t="inlineStr">
         <is>
-          <t>UAT-2 bug fixing sprint</t>
+          <t>OWASP ZAP scan + role-based access + SQLi/XSS testing</t>
         </is>
       </c>
       <c r="D120" s="7" t="n">
@@ -7653,22 +7649,22 @@
       </c>
       <c r="E120" s="7" t="inlineStr">
         <is>
-          <t>Tech Lead + Developer</t>
+          <t>Security Eng</t>
         </is>
       </c>
       <c r="F120" s="7" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
-          <t>Bhushan</t>
+          <t>Chitranshi</t>
         </is>
       </c>
       <c r="H120" s="7" t="inlineStr">
         <is>
-          <t>All UAT-2 P0/P1 defects fixed + redeployed</t>
+          <t>VAPT report - no Critical/High open findings</t>
         </is>
       </c>
       <c r="I120" s="7" t="inlineStr">
@@ -7678,14 +7674,14 @@
       </c>
       <c r="J120" s="7" t="inlineStr">
         <is>
-          <t>UAT-2</t>
+          <t>Pre-Go-Live</t>
         </is>
       </c>
       <c r="K120" s="8" t="n">
-        <v>46186</v>
+        <v>46195</v>
       </c>
       <c r="L120" s="8" t="n">
-        <v>46192</v>
+        <v>46199</v>
       </c>
       <c r="M120" s="7" t="n"/>
       <c r="N120" s="7" t="n"/>
@@ -7696,12 +7692,12 @@
       </c>
       <c r="B121" s="7" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>15.10</t>
         </is>
       </c>
       <c r="C121" s="7" t="inlineStr">
         <is>
-          <t>OWASP ZAP scan + role-based access + SQLi/XSS testing</t>
+          <t>Load test: 80 concurrent + 1200 EPs + 2000 map pins</t>
         </is>
       </c>
       <c r="D121" s="7" t="n">
@@ -7709,7 +7705,7 @@
       </c>
       <c r="E121" s="7" t="inlineStr">
         <is>
-          <t>Security Eng</t>
+          <t>QA Engineer</t>
         </is>
       </c>
       <c r="F121" s="7" t="inlineStr">
@@ -7724,7 +7720,7 @@
       </c>
       <c r="H121" s="7" t="inlineStr">
         <is>
-          <t>VAPT report - no Critical/High open findings</t>
+          <t>Page load &lt; 3s; API &lt; 1s; map renders smoothly</t>
         </is>
       </c>
       <c r="I121" s="7" t="inlineStr">
@@ -7738,125 +7734,119 @@
         </is>
       </c>
       <c r="K121" s="8" t="n">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="L121" s="8" t="n">
-        <v>46199</v>
+        <v>46206</v>
       </c>
       <c r="M121" s="7" t="n"/>
       <c r="N121" s="7" t="n"/>
     </row>
     <row r="122">
-      <c r="A122" s="7" t="n">
+      <c r="A122" s="12" t="n">
         <v>121</v>
       </c>
-      <c r="B122" s="7" t="inlineStr">
-        <is>
-          <t>15.10</t>
-        </is>
-      </c>
-      <c r="C122" s="7" t="inlineStr">
-        <is>
-          <t>Load test: 80 concurrent + 1200 EPs + 2000 map pins</t>
-        </is>
-      </c>
-      <c r="D122" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="E122" s="7" t="inlineStr">
-        <is>
-          <t>QA Engineer</t>
-        </is>
-      </c>
-      <c r="F122" s="7" t="inlineStr">
-        <is>
-          <t>15.5</t>
-        </is>
-      </c>
-      <c r="G122" s="7" t="inlineStr">
-        <is>
-          <t>Chitranshi</t>
-        </is>
-      </c>
-      <c r="H122" s="7" t="inlineStr">
-        <is>
-          <t>Page load &lt; 3s; API &lt; 1s; map renders smoothly</t>
-        </is>
-      </c>
-      <c r="I122" s="7" t="inlineStr">
+      <c r="B122" s="12" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C122" s="12" t="inlineStr">
+        <is>
+          <t>UAT &amp; Go-Live</t>
+        </is>
+      </c>
+      <c r="D122" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="E122" s="12" t="inlineStr">
+        <is>
+          <t>Developer / DevOps / PM / Client</t>
+        </is>
+      </c>
+      <c r="F122" s="12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G122" s="12" t="inlineStr">
+        <is>
+          <t>Samarth</t>
+        </is>
+      </c>
+      <c r="H122" s="12" t="inlineStr">
+        <is>
+          <t>Production cutover with MBMA sign-off + 80 fellows onboarded</t>
+        </is>
+      </c>
+      <c r="I122" s="12" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="J122" s="7" t="inlineStr">
-        <is>
-          <t>Pre-Go-Live</t>
-        </is>
-      </c>
-      <c r="K122" s="8" t="n">
-        <v>46202</v>
-      </c>
-      <c r="L122" s="8" t="n">
-        <v>46206</v>
-      </c>
-      <c r="M122" s="7" t="n"/>
-      <c r="N122" s="7" t="n"/>
+      <c r="J122" s="12" t="inlineStr">
+        <is>
+          <t>Go-Live</t>
+        </is>
+      </c>
+      <c r="K122" s="13" t="n">
+        <v>46209</v>
+      </c>
+      <c r="L122" s="13" t="n">
+        <v>46237</v>
+      </c>
+      <c r="M122" s="12" t="n"/>
+      <c r="N122" s="12" t="n"/>
     </row>
     <row r="123">
-      <c r="A123" s="12" t="n">
+      <c r="A123" s="7" t="n">
         <v>122</v>
       </c>
-      <c r="B123" s="12" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C123" s="12" t="inlineStr">
-        <is>
-          <t>UAT &amp; Go-Live</t>
-        </is>
-      </c>
-      <c r="D123" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="E123" s="12" t="inlineStr">
-        <is>
-          <t>Developer / DevOps / PM / Client</t>
-        </is>
-      </c>
-      <c r="F123" s="12" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="G123" s="12" t="inlineStr">
+      <c r="B123" s="7" t="inlineStr">
+        <is>
+          <t>16.1</t>
+        </is>
+      </c>
+      <c r="C123" s="7" t="inlineStr">
+        <is>
+          <t>UAT-3 scope finalization (post requirement gathering)</t>
+        </is>
+      </c>
+      <c r="D123" s="7" t="n"/>
+      <c r="E123" s="7" t="inlineStr">
+        <is>
+          <t>PM + Client</t>
+        </is>
+      </c>
+      <c r="F123" s="7" t="inlineStr">
+        <is>
+          <t>12.1,13.1,14.1</t>
+        </is>
+      </c>
+      <c r="G123" s="7" t="inlineStr">
         <is>
           <t>Samarth</t>
         </is>
       </c>
-      <c r="H123" s="12" t="inlineStr">
-        <is>
-          <t>Production cutover with MBMA sign-off + 80 fellows onboarded</t>
-        </is>
-      </c>
-      <c r="I123" s="12" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J123" s="12" t="inlineStr">
-        <is>
-          <t>Go-Live</t>
-        </is>
-      </c>
-      <c r="K123" s="13" t="n">
-        <v>46209</v>
-      </c>
-      <c r="L123" s="13" t="n">
-        <v>46237</v>
-      </c>
-      <c r="M123" s="12" t="n"/>
-      <c r="N123" s="12" t="n"/>
+      <c r="H123" s="7" t="inlineStr">
+        <is>
+          <t>UAT-3 scope: Intervention Dashboard + Apoorva AI + Claude Chatbot - dates set once specs sign off</t>
+        </is>
+      </c>
+      <c r="I123" s="7" t="inlineStr">
+        <is>
+          <t>Pending Requirements</t>
+        </is>
+      </c>
+      <c r="J123" s="7" t="inlineStr">
+        <is>
+          <t>UAT-3</t>
+        </is>
+      </c>
+      <c r="K123" s="7" t="n"/>
+      <c r="L123" s="7" t="n"/>
+      <c r="M123" s="7" t="n"/>
+      <c r="N123" s="7" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="7" t="n">
@@ -7864,47 +7854,53 @@
       </c>
       <c r="B124" s="7" t="inlineStr">
         <is>
-          <t>16.1</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
-          <t>UAT-3 scope finalization (post requirement gathering)</t>
-        </is>
-      </c>
-      <c r="D124" s="7" t="n"/>
+          <t>Production environment setup + SSL + domain</t>
+        </is>
+      </c>
+      <c r="D124" s="7" t="n">
+        <v>5</v>
+      </c>
       <c r="E124" s="7" t="inlineStr">
         <is>
-          <t>PM + Client</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="F124" s="7" t="inlineStr">
         <is>
-          <t>12.1,13.1,14.1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
-          <t>Samarth</t>
+          <t>Prakash</t>
         </is>
       </c>
       <c r="H124" s="7" t="inlineStr">
         <is>
-          <t>UAT-3 scope: Intervention Dashboard + Apoorva AI + Claude Chatbot - dates set once specs sign off</t>
+          <t>prime-rural.dhwaniris.in live with HTTPS + backups configured</t>
         </is>
       </c>
       <c r="I124" s="7" t="inlineStr">
         <is>
-          <t>Pending Requirements</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="J124" s="7" t="inlineStr">
         <is>
-          <t>UAT-3</t>
-        </is>
-      </c>
-      <c r="K124" s="7" t="n"/>
-      <c r="L124" s="7" t="n"/>
+          <t>Go-Live</t>
+        </is>
+      </c>
+      <c r="K124" s="8" t="n">
+        <v>46209</v>
+      </c>
+      <c r="L124" s="8" t="n">
+        <v>46213</v>
+      </c>
       <c r="M124" s="7" t="n"/>
       <c r="N124" s="7" t="n"/>
     </row>
@@ -7914,12 +7910,12 @@
       </c>
       <c r="B125" s="7" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="C125" s="7" t="inlineStr">
         <is>
-          <t>Production environment setup + SSL + domain</t>
+          <t>Data migration: Google Sheets -&gt; Frappe</t>
         </is>
       </c>
       <c r="D125" s="7" t="n">
@@ -7927,22 +7923,22 @@
       </c>
       <c r="E125" s="7" t="inlineStr">
         <is>
-          <t>DevOps</t>
+          <t>Backend Dev</t>
         </is>
       </c>
       <c r="F125" s="7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16.2</t>
         </is>
       </c>
       <c r="G125" s="7" t="inlineStr">
         <is>
-          <t>Prakash</t>
+          <t>Navneet</t>
         </is>
       </c>
       <c r="H125" s="7" t="inlineStr">
         <is>
-          <t>prime-rural.dhwaniris.in live with HTTPS + backups configured</t>
+          <t>Legacy 32-framework data + entrepreneur records migrated + validated</t>
         </is>
       </c>
       <c r="I125" s="7" t="inlineStr">
@@ -7956,10 +7952,10 @@
         </is>
       </c>
       <c r="K125" s="8" t="n">
-        <v>46209</v>
+        <v>46216</v>
       </c>
       <c r="L125" s="8" t="n">
-        <v>46213</v>
+        <v>46220</v>
       </c>
       <c r="M125" s="7" t="n"/>
       <c r="N125" s="7" t="n"/>
@@ -7970,12 +7966,12 @@
       </c>
       <c r="B126" s="7" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="C126" s="7" t="inlineStr">
         <is>
-          <t>Data migration: Google Sheets -&gt; Frappe</t>
+          <t>User onboarding: 80 fellows + coordinators</t>
         </is>
       </c>
       <c r="D126" s="7" t="n">
@@ -7983,22 +7979,22 @@
       </c>
       <c r="E126" s="7" t="inlineStr">
         <is>
-          <t>Backend Dev</t>
+          <t>PM</t>
         </is>
       </c>
       <c r="F126" s="7" t="inlineStr">
         <is>
-          <t>16.2</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
-          <t>Navneet</t>
+          <t>Samarth</t>
         </is>
       </c>
       <c r="H126" s="7" t="inlineStr">
         <is>
-          <t>Legacy 32-framework data + entrepreneur records migrated + validated</t>
+          <t>All users invited; passwords set; first login captured</t>
         </is>
       </c>
       <c r="I126" s="7" t="inlineStr">
@@ -8012,10 +8008,10 @@
         </is>
       </c>
       <c r="K126" s="8" t="n">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="L126" s="8" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="M126" s="7" t="n"/>
       <c r="N126" s="7" t="n"/>
@@ -8026,12 +8022,12 @@
       </c>
       <c r="B127" s="7" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>16.5</t>
         </is>
       </c>
       <c r="C127" s="7" t="inlineStr">
         <is>
-          <t>User onboarding: 80 fellows + coordinators</t>
+          <t>Training sessions for field users (Fessociates + Coordinators)</t>
         </is>
       </c>
       <c r="D127" s="7" t="n">
@@ -8044,7 +8040,7 @@
       </c>
       <c r="F127" s="7" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="G127" s="7" t="inlineStr">
@@ -8054,7 +8050,7 @@
       </c>
       <c r="H127" s="7" t="inlineStr">
         <is>
-          <t>All users invited; passwords set; first login captured</t>
+          <t>All 80 users trained; recordings shared; FAQ doc published</t>
         </is>
       </c>
       <c r="I127" s="7" t="inlineStr">
@@ -8068,10 +8064,10 @@
         </is>
       </c>
       <c r="K127" s="8" t="n">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="L127" s="8" t="n">
-        <v>46227</v>
+        <v>46234</v>
       </c>
       <c r="M127" s="7" t="n"/>
       <c r="N127" s="7" t="n"/>
@@ -8082,27 +8078,27 @@
       </c>
       <c r="B128" s="7" t="inlineStr">
         <is>
+          <t>16.6</t>
+        </is>
+      </c>
+      <c r="C128" s="7" t="inlineStr">
+        <is>
+          <t>Go-live sign-off from MBMA</t>
+        </is>
+      </c>
+      <c r="D128" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" s="7" t="inlineStr">
+        <is>
+          <t>PM + Client</t>
+        </is>
+      </c>
+      <c r="F128" s="7" t="inlineStr">
+        <is>
           <t>16.5</t>
         </is>
       </c>
-      <c r="C128" s="7" t="inlineStr">
-        <is>
-          <t>Training sessions for field users (Fessociates + Coordinators)</t>
-        </is>
-      </c>
-      <c r="D128" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="E128" s="7" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="F128" s="7" t="inlineStr">
-        <is>
-          <t>16.4</t>
-        </is>
-      </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
           <t>Samarth</t>
@@ -8110,7 +8106,7 @@
       </c>
       <c r="H128" s="7" t="inlineStr">
         <is>
-          <t>All 80 users trained; recordings shared; FAQ doc published</t>
+          <t>Signed handover note + MoM filed</t>
         </is>
       </c>
       <c r="I128" s="7" t="inlineStr">
@@ -8124,72 +8120,16 @@
         </is>
       </c>
       <c r="K128" s="8" t="n">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="L128" s="8" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="M128" s="7" t="n"/>
       <c r="N128" s="7" t="n"/>
     </row>
-    <row r="129">
-      <c r="A129" s="7" t="n">
-        <v>128</v>
-      </c>
-      <c r="B129" s="7" t="inlineStr">
-        <is>
-          <t>16.6</t>
-        </is>
-      </c>
-      <c r="C129" s="7" t="inlineStr">
-        <is>
-          <t>Go-live sign-off from MBMA</t>
-        </is>
-      </c>
-      <c r="D129" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E129" s="7" t="inlineStr">
-        <is>
-          <t>PM + Client</t>
-        </is>
-      </c>
-      <c r="F129" s="7" t="inlineStr">
-        <is>
-          <t>16.5</t>
-        </is>
-      </c>
-      <c r="G129" s="7" t="inlineStr">
-        <is>
-          <t>Samarth</t>
-        </is>
-      </c>
-      <c r="H129" s="7" t="inlineStr">
-        <is>
-          <t>Signed handover note + MoM filed</t>
-        </is>
-      </c>
-      <c r="I129" s="7" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="J129" s="7" t="inlineStr">
-        <is>
-          <t>Go-Live</t>
-        </is>
-      </c>
-      <c r="K129" s="8" t="n">
-        <v>46237</v>
-      </c>
-      <c r="L129" s="8" t="n">
-        <v>46237</v>
-      </c>
-      <c r="M129" s="7" t="n"/>
-      <c r="N129" s="7" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:N129"/>
+  <autoFilter ref="A1:N128"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8530,9 +8470,9 @@
           <t>11. Milestone &amp; Activity Tracker</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>Completed</t>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
@@ -8865,7 +8805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9042,6 +8982,39 @@
       </c>
       <c r="G5" s="20" t="inlineStr">
         <is>
+          <t>Superseded</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>v6.1</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="n">
+        <v>46182</v>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>Status reconciliation against the 7-8 Jun internal UAT-1 E2E run (272 cases, ~60 bugs) + the Jun 1-3 dev sprint. User Management (2.1/2.2) -&gt; Completed (verified). UAT-1 test scripts (15.2) -&gt; Completed; internal dry run (15.3) -&gt; In Progress (executed, 3 P1 fixes pending). Prototyping (6.10) and Milestone Tracker (11/11.1/11.3) -&gt; In Progress after P1 regressions (Bug 54 save-500, Bug 55 dashboard non-functional). No new rows.</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>Samarth (PM) + Claude</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>Pending MBMA review</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
           <t>Published</t>
         </is>
       </c>
